--- a/Benchtop-2024(default-version)/parts-list/Benchtop-partslist-latest.xlsx
+++ b/Benchtop-2024(default-version)/parts-list/Benchtop-partslist-latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikita\Documents\GitHub\mesoSPIM-bt-hardware\Benchtop-2024(default-version)\parts-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406209C3-3B8A-4E04-9253-1DAB197978EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A86552-FCF6-45BC-9F72-AEE6E4726460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12492" yWindow="4404" windowWidth="28728" windowHeight="16980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13584" yWindow="5808" windowWidth="32100" windowHeight="16548" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="626">
   <si>
     <t xml:space="preserve">Part # </t>
   </si>
@@ -1949,11 +1949,25 @@
     <t>The cable MUST be "-EPM". Other similarly looking cables with marking "-RDIO" are NOT suitable.</t>
   </si>
   <si>
+    <t>Legacy:</t>
+  </si>
+  <si>
+    <t>Currently recommended:</t>
+  </si>
+  <si>
+    <t>TOPTICA</t>
+  </si>
+  <si>
+    <t>CLE-50 combiner (405nm, 488nm, 561nm, 640nm: 50 mW each)</t>
+  </si>
+  <si>
+    <t>Typically very stable and reliable lasers. For more budget lasers, CLE-20 or CLE-30 (20 and 30 mW per chanel) can be considered.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -1962,11 +1976,10 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> this is a budget laser, with relatively frequent quality issues. See overview at (https://github.com/mesoSPIM/benchtop-hardware/wiki/Laser-selection). Includes switching module between 2 laser ports, controlled by TTL signal. The 405nm is NOT included! A four-laser version is ~35k.</t>
+      <t xml:space="preserve"> Oxxius is a budget laser, with frequent quality issues. See overview at (https://github.com/mesoSPIM/benchtop-hardware/wiki/Laser-selection). Includes switching module between 2 laser ports, controlled by TTL signal. The 405nm is NOT included! A four-laser version is ~35k.</t>
     </r>
   </si>
 </sst>
@@ -1974,7 +1987,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2146,6 +2159,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2253,7 +2272,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
@@ -2353,6 +2372,10 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="4" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="1" fontId="9" fillId="9" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="4" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="4" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Excel Built-in Heading 1" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2740,7 +2763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J208"/>
+  <dimension ref="A1:J209"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5546875" style="3" customWidth="1"/>
@@ -2846,133 +2869,136 @@
       <c r="E7" s="56"/>
       <c r="F7" s="56"/>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:9" s="87" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="87" t="s">
+        <v>621</v>
+      </c>
+      <c r="B8" s="87" t="s">
+        <v>622</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>623</v>
+      </c>
+      <c r="D8" s="87">
+        <v>2</v>
+      </c>
+      <c r="E8" s="88">
+        <v>29000</v>
+      </c>
+      <c r="F8" s="88">
+        <f>D8*E8</f>
+        <v>58000</v>
+      </c>
+      <c r="G8" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="87" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="89" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="89" t="s">
+        <v>620</v>
+      </c>
+      <c r="B9" s="89" t="s">
         <v>161</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="89" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="55">
+      <c r="D9" s="89">
+        <v>0</v>
+      </c>
+      <c r="E9" s="90">
         <v>25000</v>
       </c>
-      <c r="F8" s="55">
-        <f>D8*E8</f>
-        <v>25000</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="F9" s="90">
+        <f>D9*E9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="I9" s="19" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-    </row>
-    <row r="10" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
-        <v>597</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="D10" s="28">
-        <v>0</v>
-      </c>
-      <c r="E10" s="43">
-        <v>6500</v>
-      </c>
-      <c r="F10" s="43">
-        <f t="shared" ref="F10:F27" si="0">E10*D10</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>211</v>
-      </c>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
     </row>
     <row r="11" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>19</v>
+        <v>597</v>
       </c>
       <c r="B11" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>20</v>
+        <v>395</v>
       </c>
       <c r="D11" s="28">
         <v>0</v>
       </c>
       <c r="E11" s="43">
-        <v>2250</v>
+        <v>6500</v>
       </c>
       <c r="F11" s="43">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F11:F28" si="0">E11*D11</f>
         <v>0</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>219</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="28">
         <v>0</v>
       </c>
       <c r="E12" s="43">
-        <v>160</v>
+        <v>2250</v>
       </c>
       <c r="F12" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>13</v>
+        <v>219</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D13" s="28">
         <v>0</v>
       </c>
       <c r="E13" s="43">
-        <v>2250</v>
+        <v>160</v>
       </c>
       <c r="F13" s="43">
         <f t="shared" si="0"/>
@@ -2984,52 +3010,52 @@
       <c r="H13" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="28" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="14" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D14" s="28">
         <v>0</v>
       </c>
       <c r="E14" s="43">
-        <v>230</v>
+        <v>2250</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>219</v>
+        <v>214</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>13</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>598</v>
+        <v>24</v>
       </c>
       <c r="B15" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="28">
         <v>0</v>
       </c>
       <c r="E15" s="43">
-        <v>2425</v>
+        <v>230</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="0"/>
@@ -3039,24 +3065,24 @@
         <v>219</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>392</v>
+        <v>598</v>
       </c>
       <c r="B16" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>393</v>
+        <v>26</v>
       </c>
       <c r="D16" s="28">
         <v>0</v>
       </c>
       <c r="E16" s="43">
-        <v>3000</v>
+        <v>2425</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="0"/>
@@ -3066,24 +3092,24 @@
         <v>219</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>394</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>27</v>
+        <v>392</v>
       </c>
       <c r="B17" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
       <c r="D17" s="28">
         <v>0</v>
       </c>
       <c r="E17" s="43">
-        <v>150</v>
+        <v>3000</v>
       </c>
       <c r="F17" s="43">
         <f t="shared" si="0"/>
@@ -3093,108 +3119,108 @@
         <v>219</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>220</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="53" t="s">
-        <v>29</v>
+      <c r="A18" s="28" t="s">
+        <v>27</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D18" s="28">
         <v>0</v>
       </c>
       <c r="E18" s="43">
-        <v>3000</v>
+        <v>150</v>
       </c>
       <c r="F18" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G18" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="28">
+        <v>0</v>
+      </c>
+      <c r="E19" s="43">
+        <v>3000</v>
+      </c>
+      <c r="F19" s="43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="I19" s="28" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="E19" s="58">
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="58">
         <v>19965</v>
       </c>
-      <c r="F19" s="58">
+      <c r="F20" s="58">
         <f t="shared" si="0"/>
         <v>19965</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
         <v>31</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="D21" s="28">
-        <v>0</v>
-      </c>
-      <c r="E21" s="43">
-        <v>5800</v>
-      </c>
-      <c r="F21" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="I21" s="28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
-        <v>599</v>
       </c>
       <c r="B22" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="D22" s="28">
         <v>0</v>
       </c>
       <c r="E22" s="43">
-        <v>1100</v>
+        <v>5800</v>
       </c>
       <c r="F22" s="43">
         <f t="shared" si="0"/>
@@ -3204,588 +3230,585 @@
         <v>218</v>
       </c>
       <c r="I22" s="28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="53" t="s">
+        <v>599</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>600</v>
+      </c>
+      <c r="D23" s="28">
+        <v>0</v>
+      </c>
+      <c r="E23" s="43">
+        <v>1100</v>
+      </c>
+      <c r="F23" s="43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="I23" s="28" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="58">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="58">
         <v>6900</v>
       </c>
-      <c r="F23" s="58">
+      <c r="F24" s="58">
         <f t="shared" si="0"/>
         <v>6900</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-    </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
-      <c r="E25" s="58">
-        <v>160</v>
-      </c>
-      <c r="F25" s="58">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>578</v>
-      </c>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="58">
+        <v>160</v>
+      </c>
+      <c r="F26" s="58">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B27" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D27" s="4">
         <v>0</v>
       </c>
-      <c r="E26" s="58">
+      <c r="E27" s="58">
         <v>1740</v>
       </c>
-      <c r="F26" s="58">
+      <c r="F27" s="58">
         <v>1740</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I27" s="4" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="B28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D28" s="3">
         <v>5</v>
       </c>
-      <c r="E27" s="55">
+      <c r="E28" s="55">
         <v>27</v>
       </c>
-      <c r="F27" s="55">
+      <c r="F28" s="55">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+    <row r="29" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D29" s="3">
-        <v>2</v>
-      </c>
-      <c r="E29" s="55">
-        <v>70</v>
-      </c>
-      <c r="F29" s="55">
-        <f t="shared" ref="F29:F36" si="1">E29*D29</f>
-        <v>140</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>234</v>
-      </c>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2</v>
+      </c>
+      <c r="E30" s="55">
+        <v>70</v>
+      </c>
+      <c r="F30" s="55">
+        <f t="shared" ref="F30:F37" si="1">E30*D30</f>
+        <v>140</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="B31" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D31" s="3">
         <v>6</v>
       </c>
-      <c r="E30" s="55">
+      <c r="E31" s="55">
         <v>36</v>
       </c>
-      <c r="F30" s="55">
+      <c r="F31" s="55">
         <f t="shared" si="1"/>
         <v>216</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
-        <v>476</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D31" s="3">
-        <v>1</v>
-      </c>
-      <c r="E31" s="55">
-        <v>6</v>
-      </c>
-      <c r="F31" s="55">
-        <f>D31*E31</f>
-        <v>6</v>
-      </c>
       <c r="G31" s="3" t="s">
         <v>237</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>595</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
       </c>
       <c r="E32" s="55">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F32" s="55">
         <f>D32*E32</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>237</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1</v>
+      </c>
+      <c r="E33" s="55">
+        <v>9</v>
+      </c>
+      <c r="F33" s="55">
+        <f>D33*E33</f>
+        <v>9</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="B34" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D33" s="3">
-        <v>1</v>
-      </c>
-      <c r="E33" s="55">
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="55">
         <v>43</v>
       </c>
-      <c r="F33" s="55">
+      <c r="F34" s="55">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G34" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I34" s="3" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="B35" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
-      <c r="E34" s="55">
+      <c r="D35" s="3">
+        <v>1</v>
+      </c>
+      <c r="E35" s="55">
         <v>29</v>
       </c>
-      <c r="F34" s="55">
+      <c r="F35" s="55">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I35" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B36" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D35" s="3">
-        <v>1</v>
-      </c>
-      <c r="E35" s="55">
+      <c r="D36" s="3">
+        <v>1</v>
+      </c>
+      <c r="E36" s="55">
         <v>195</v>
       </c>
-      <c r="F35" s="55">
+      <c r="F36" s="55">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G36" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I36" s="3" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="82" t="s">
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="82" t="s">
         <v>592</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B37" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C37" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="D36" s="4">
-        <v>1</v>
-      </c>
-      <c r="E36" s="58">
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="58">
         <v>10</v>
       </c>
-      <c r="F36" s="58">
+      <c r="F37" s="58">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I37" s="4" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="12" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
+    <row r="38" spans="1:9" s="12" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
         <v>32</v>
-      </c>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-    </row>
-    <row r="38" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="86" t="s">
-        <v>618</v>
       </c>
       <c r="E38" s="59"/>
       <c r="F38" s="59"/>
     </row>
-    <row r="39" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="83" t="s">
-        <v>604</v>
-      </c>
-      <c r="B39" s="83" t="s">
-        <v>609</v>
-      </c>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85"/>
+    <row r="39" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="86" t="s">
+        <v>618</v>
+      </c>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
     </row>
     <row r="40" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="83" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B40" s="83" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E40" s="85"/>
       <c r="F40" s="85"/>
     </row>
     <row r="41" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="83" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B41" s="83" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
     </row>
     <row r="42" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="83" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B42" s="83" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="E42" s="85"/>
       <c r="F42" s="85"/>
     </row>
     <row r="43" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="83" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="B43" s="83" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E43" s="85"/>
       <c r="F43" s="85"/>
     </row>
     <row r="44" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="83" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="B44" s="83" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="E44" s="85"/>
       <c r="F44" s="85"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="83" t="s">
+        <v>616</v>
+      </c>
+      <c r="B45" s="83" t="s">
+        <v>617</v>
+      </c>
+      <c r="E45" s="85"/>
+      <c r="F45" s="85"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+    <row r="47" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-    </row>
-    <row r="47" spans="1:9" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="75" t="s">
-        <v>493</v>
-      </c>
-      <c r="B47" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="40" t="s">
-        <v>492</v>
-      </c>
-      <c r="D47" s="40">
-        <v>1</v>
-      </c>
-      <c r="E47" s="74">
-        <v>728</v>
-      </c>
-      <c r="F47" s="74">
-        <f>D47*E47</f>
-        <v>728</v>
-      </c>
-      <c r="G47" s="40" t="s">
-        <v>491</v>
-      </c>
-      <c r="I47" s="40" t="s">
-        <v>494</v>
-      </c>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
     </row>
     <row r="48" spans="1:9" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="75" t="s">
-        <v>544</v>
+        <v>493</v>
       </c>
       <c r="B48" s="40" t="s">
         <v>54</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>543</v>
+        <v>492</v>
       </c>
       <c r="D48" s="40">
         <v>1</v>
       </c>
       <c r="E48" s="74">
-        <v>33</v>
+        <v>728</v>
       </c>
       <c r="F48" s="74">
-        <v>33</v>
+        <f>D48*E48</f>
+        <v>728</v>
       </c>
       <c r="G48" s="40" t="s">
         <v>491</v>
       </c>
       <c r="I48" s="40" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="75" t="s">
+        <v>544</v>
+      </c>
+      <c r="B49" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="40" t="s">
+        <v>543</v>
+      </c>
+      <c r="D49" s="40">
+        <v>1</v>
+      </c>
+      <c r="E49" s="74">
+        <v>33</v>
+      </c>
+      <c r="F49" s="74">
+        <v>33</v>
+      </c>
+      <c r="G49" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="I49" s="40" t="s">
         <v>545</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="D49" s="3">
-        <v>2</v>
-      </c>
-      <c r="E49" s="57">
-        <v>31</v>
-      </c>
-      <c r="F49" s="55">
-        <f t="shared" ref="F49:F54" si="2">E49*D49</f>
-        <v>62</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H49" s="77" t="s">
-        <v>181</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>179</v>
+        <v>62</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D50" s="3">
         <v>2</v>
       </c>
       <c r="E50" s="57">
+        <v>31</v>
+      </c>
+      <c r="F50" s="55">
+        <f t="shared" ref="F50:F55" si="2">E50*D50</f>
+        <v>62</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" s="3">
+        <v>2</v>
+      </c>
+      <c r="E51" s="57">
         <v>99</v>
       </c>
-      <c r="F50" s="55">
+      <c r="F51" s="55">
         <f t="shared" si="2"/>
         <v>198</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G51" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="77" t="s">
+      <c r="H51" s="77" t="s">
         <v>181</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I51" s="3" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="B52" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D52" s="3">
         <v>2</v>
       </c>
-      <c r="E51" s="55">
+      <c r="E52" s="55">
         <v>17</v>
       </c>
-      <c r="F51" s="55">
+      <c r="F52" s="55">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H51" s="77" t="s">
-        <v>181</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="D52" s="3">
-        <v>2</v>
-      </c>
-      <c r="E52" s="55">
-        <v>12</v>
-      </c>
-      <c r="F52" s="55">
-        <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>34</v>
       </c>
@@ -3793,18 +3816,18 @@
         <v>181</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D53" s="3">
         <v>2</v>
@@ -3823,28 +3846,28 @@
         <v>181</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>188</v>
+        <v>520</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D54" s="3">
         <v>2</v>
       </c>
       <c r="E54" s="55">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F54" s="55">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>34</v>
@@ -3853,195 +3876,198 @@
         <v>181</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>273</v>
+        <v>188</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>469</v>
+        <v>522</v>
       </c>
       <c r="D55" s="3">
         <v>2</v>
       </c>
       <c r="E55" s="55">
-        <v>18.412749600000001</v>
+        <v>14</v>
       </c>
       <c r="F55" s="55">
-        <v>36.825499200000003</v>
+        <f t="shared" si="2"/>
+        <v>28</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H55" s="3" t="s">
-        <v>470</v>
+      <c r="H55" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>293</v>
+        <v>54</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D56" s="3">
         <v>2</v>
       </c>
       <c r="E56" s="55">
-        <v>935</v>
+        <v>18.412749600000001</v>
       </c>
       <c r="F56" s="55">
-        <f t="shared" ref="F56:F62" si="3">E56*D56</f>
-        <v>1870</v>
+        <v>36.825499200000003</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H56" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D57" s="3">
+        <v>2</v>
+      </c>
+      <c r="E57" s="55">
+        <v>935</v>
+      </c>
+      <c r="F57" s="55">
+        <f t="shared" ref="F57:F63" si="3">E57*D57</f>
+        <v>1870</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
+    <row r="58" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B58" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C58" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D58" s="4">
         <v>2</v>
       </c>
-      <c r="E57" s="58">
+      <c r="E58" s="58">
         <v>365</v>
       </c>
-      <c r="F57" s="58">
+      <c r="F58" s="58">
         <f t="shared" si="3"/>
         <v>730</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I57" s="4" t="s">
+      <c r="I58" s="4" t="s">
         <v>468</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="D58" s="3">
-        <v>1</v>
-      </c>
-      <c r="E58" s="55">
-        <v>40</v>
-      </c>
-      <c r="F58" s="55">
-        <f>D58*E58</f>
-        <v>40</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="D59" s="3">
+        <v>1</v>
+      </c>
+      <c r="E59" s="55">
+        <v>40</v>
+      </c>
+      <c r="F59" s="55">
+        <f>D59*E59</f>
+        <v>40</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B60" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D60" s="3">
         <v>2</v>
       </c>
-      <c r="E59" s="55">
+      <c r="E60" s="55">
         <v>90</v>
       </c>
-      <c r="F59" s="55">
+      <c r="F60" s="55">
         <f t="shared" si="3"/>
         <v>180</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D60" s="3">
-        <v>2</v>
-      </c>
-      <c r="E60" s="57">
-        <v>18</v>
-      </c>
-      <c r="F60" s="55">
-        <f>E60*D60</f>
-        <v>36</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>470</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>69</v>
+      <c r="A61" s="9" t="s">
+        <v>489</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>70</v>
+      <c r="C61" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="D61" s="3">
         <v>2</v>
       </c>
-      <c r="E61" s="55">
-        <v>21.21</v>
+      <c r="E61" s="57">
+        <v>18</v>
       </c>
       <c r="F61" s="55">
-        <f t="shared" ref="F61" si="4">E61*D61</f>
-        <v>42.42</v>
+        <f>E61*D61</f>
+        <v>36</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>34</v>
@@ -4049,770 +4075,767 @@
       <c r="H61" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="I61" s="3" t="s">
-        <v>471</v>
-      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
-        <v>188</v>
+      <c r="A62" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C62" s="9" t="s">
-        <v>189</v>
+      <c r="C62" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="D62" s="3">
         <v>2</v>
       </c>
-      <c r="E62" s="57">
+      <c r="E62" s="55">
+        <v>21.21</v>
+      </c>
+      <c r="F62" s="55">
+        <f t="shared" ref="F62" si="4">E62*D62</f>
+        <v>42.42</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D63" s="3">
+        <v>2</v>
+      </c>
+      <c r="E63" s="57">
         <v>13</v>
       </c>
-      <c r="F62" s="55">
+      <c r="F63" s="55">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="D63" s="3">
-        <v>4</v>
-      </c>
-      <c r="E63" s="57">
-        <v>189</v>
-      </c>
-      <c r="F63" s="55">
-        <f t="shared" ref="F63:F70" si="5">E63*D63</f>
-        <v>756</v>
-      </c>
       <c r="G63" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>272</v>
+        <v>470</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D64" s="3">
         <v>4</v>
       </c>
       <c r="E64" s="57">
+        <v>189</v>
+      </c>
+      <c r="F64" s="55">
+        <f t="shared" ref="F64:F71" si="5">E64*D64</f>
+        <v>756</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D65" s="3">
+        <v>4</v>
+      </c>
+      <c r="E65" s="57">
         <v>110</v>
       </c>
-      <c r="F64" s="55">
+      <c r="F65" s="55">
         <f t="shared" si="5"/>
         <v>440</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G65" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="H65" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="I65" s="3" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C65" s="9" t="s">
+      <c r="B66" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D66" s="3">
         <v>8</v>
       </c>
-      <c r="E65" s="57">
+      <c r="E66" s="57">
         <v>16</v>
       </c>
-      <c r="F65" s="55">
+      <c r="F66" s="55">
         <f t="shared" si="5"/>
         <v>128</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G66" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I66" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C66" s="9" t="s">
+      <c r="B67" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D67" s="3">
         <v>4</v>
       </c>
-      <c r="E66" s="57">
+      <c r="E67" s="57">
         <v>104</v>
       </c>
-      <c r="F66" s="55">
+      <c r="F67" s="55">
         <f t="shared" si="5"/>
         <v>416</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G67" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="H67" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="I67" s="3" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="s">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C67" s="9" t="s">
+      <c r="B68" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D68" s="3">
         <v>2</v>
       </c>
-      <c r="E67" s="57">
+      <c r="E68" s="57">
         <v>41</v>
       </c>
-      <c r="F67" s="55">
+      <c r="F68" s="55">
         <f t="shared" si="5"/>
         <v>82</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G68" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I68" s="3" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C68" s="9" t="s">
+      <c r="B69" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D69" s="3">
         <v>2</v>
       </c>
-      <c r="E68" s="57">
+      <c r="E69" s="57">
         <v>17</v>
       </c>
-      <c r="F68" s="55">
+      <c r="F69" s="55">
         <f t="shared" si="5"/>
         <v>34</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G69" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="I69" s="3" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C69" s="9" t="s">
+      <c r="B70" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D70" s="3">
         <v>4</v>
       </c>
-      <c r="E69" s="57">
+      <c r="E70" s="57">
         <v>7</v>
       </c>
-      <c r="F69" s="55">
+      <c r="F70" s="55">
         <f t="shared" si="5"/>
         <v>28</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G70" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="H70" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="I70" s="3" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C70" s="9" t="s">
+      <c r="B71" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D71" s="3">
         <v>4</v>
       </c>
-      <c r="E70" s="57">
+      <c r="E71" s="57">
         <v>5</v>
       </c>
-      <c r="F70" s="55">
+      <c r="F71" s="55">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G71" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H71" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="I71" s="3" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="71" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="47">
+    <row r="72" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="47">
         <v>91863</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B72" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C72" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="D71" s="4">
-        <v>2</v>
-      </c>
-      <c r="E71" s="58">
-        <v>400</v>
-      </c>
-      <c r="F71" s="58">
-        <f t="shared" ref="F71:F94" si="6">E71*D71</f>
-        <v>800</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="C72" s="48" t="s">
-        <v>498</v>
       </c>
       <c r="D72" s="4">
         <v>2</v>
       </c>
       <c r="E72" s="58">
+        <v>400</v>
+      </c>
+      <c r="F72" s="58">
+        <f t="shared" ref="F72:F95" si="6">E72*D72</f>
+        <v>800</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C73" s="48" t="s">
+        <v>498</v>
+      </c>
+      <c r="D73" s="4">
+        <v>2</v>
+      </c>
+      <c r="E73" s="58">
         <v>300</v>
       </c>
-      <c r="F72" s="58">
+      <c r="F73" s="58">
         <f t="shared" si="6"/>
         <v>600</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="G73" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H72" s="4" t="s">
+      <c r="H73" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="I72" s="4" t="s">
+      <c r="I73" s="4" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="44" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="45" t="s">
+    <row r="74" spans="1:10" s="44" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="45" t="s">
         <v>400</v>
       </c>
-      <c r="B73" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="C73" s="45" t="s">
+      <c r="B74" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C74" s="45" t="s">
         <v>397</v>
       </c>
-      <c r="D73" s="44">
+      <c r="D74" s="44">
         <v>0</v>
       </c>
-      <c r="E73" s="63">
+      <c r="E74" s="63">
         <v>36</v>
       </c>
-      <c r="F73" s="64">
+      <c r="F74" s="64">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G73" s="44" t="s">
+      <c r="G74" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="H73" s="44" t="s">
+      <c r="H74" s="44" t="s">
         <v>207</v>
       </c>
-      <c r="I73" s="44" t="s">
+      <c r="I74" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="J73" s="73"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="s">
+      <c r="J74" s="73"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C74" s="9" t="s">
+      <c r="B75" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D75" s="3">
         <v>2</v>
       </c>
-      <c r="E74" s="57">
+      <c r="E75" s="57">
         <v>92</v>
       </c>
-      <c r="F74" s="55">
+      <c r="F75" s="55">
         <f t="shared" si="6"/>
         <v>184</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="G75" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H74" s="3" t="s">
+      <c r="H75" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="I75" s="3" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="10" t="s">
+    <row r="76" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B76" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C75" s="72" t="s">
+      <c r="C76" s="72" t="s">
         <v>249</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D76" s="4">
         <v>2</v>
       </c>
-      <c r="E75" s="60">
-        <v>1</v>
-      </c>
-      <c r="F75" s="58">
+      <c r="E76" s="60">
+        <v>1</v>
+      </c>
+      <c r="F76" s="58">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H75" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="I75" s="4" t="s">
+      <c r="I76" s="4" t="s">
         <v>594</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="D76" s="3">
-        <v>4</v>
-      </c>
-      <c r="E76" s="57">
-        <v>7</v>
-      </c>
-      <c r="F76" s="55">
-        <f>E76*D76</f>
-        <v>28</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="D77" s="3">
+        <v>4</v>
+      </c>
+      <c r="E77" s="57">
+        <v>7</v>
+      </c>
+      <c r="F77" s="55">
+        <f>E77*D77</f>
+        <v>28</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C77" s="9" t="s">
+      <c r="B78" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C78" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D78" s="3">
         <v>2</v>
       </c>
-      <c r="E77" s="57">
+      <c r="E78" s="57">
         <v>8</v>
       </c>
-      <c r="F77" s="55">
+      <c r="F78" s="55">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G78" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="H78" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C78" s="9" t="s">
+      <c r="B79" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D79" s="3">
         <v>4</v>
       </c>
-      <c r="E78" s="57">
+      <c r="E79" s="57">
         <v>5</v>
       </c>
-      <c r="F78" s="55">
+      <c r="F79" s="55">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G79" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H79" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="I78" s="3" t="s">
+      <c r="I79" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C79" s="9" t="s">
+      <c r="B80" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C80" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D80" s="3">
         <v>2</v>
       </c>
-      <c r="E79" s="57">
+      <c r="E80" s="57">
         <v>5</v>
       </c>
-      <c r="F79" s="55">
+      <c r="F80" s="55">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D80" s="3">
-        <v>2</v>
-      </c>
-      <c r="E80" s="57">
-        <v>5</v>
-      </c>
-      <c r="F80" s="55">
-        <f>E80*D80</f>
-        <v>10</v>
-      </c>
       <c r="G80" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I80" s="3" t="s">
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D81" s="3">
+        <v>2</v>
+      </c>
+      <c r="E81" s="57">
+        <v>5</v>
+      </c>
+      <c r="F81" s="55">
+        <f>E81*D81</f>
+        <v>10</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I81" s="3" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="81" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="22" t="s">
+    <row r="82" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="22" t="s">
         <v>490</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C81" s="22" t="s">
+      <c r="B82" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C82" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="D81" s="23">
+      <c r="D82" s="23">
         <v>2</v>
       </c>
-      <c r="E81" s="61">
+      <c r="E82" s="61">
         <v>398</v>
       </c>
-      <c r="F81" s="62">
+      <c r="F82" s="62">
         <f t="shared" si="6"/>
         <v>796</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G82" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H81" s="23" t="s">
+      <c r="H82" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="I81" s="23" t="s">
+      <c r="I82" s="23" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="82" spans="1:9" s="78" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A82" s="46" t="s">
+    <row r="83" spans="1:9" s="78" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="46" t="s">
         <v>535</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B83" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C82" s="46" t="s">
+      <c r="C83" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="D82" s="78">
+      <c r="D83" s="78">
         <v>2</v>
       </c>
-      <c r="E82" s="79">
+      <c r="E83" s="79">
         <v>150</v>
       </c>
-      <c r="F82" s="80">
+      <c r="F83" s="80">
         <v>0</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G83" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H82" s="78" t="s">
+      <c r="H83" s="78" t="s">
         <v>202</v>
       </c>
-      <c r="I82" s="78" t="s">
+      <c r="I83" s="78" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="83" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="22" t="s">
+    <row r="84" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C83" s="22" t="s">
+      <c r="B84" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C84" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="D83" s="23">
+      <c r="D84" s="23">
         <v>2</v>
       </c>
-      <c r="E83" s="61">
+      <c r="E84" s="61">
         <v>30</v>
       </c>
-      <c r="F83" s="62">
+      <c r="F84" s="62">
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="G84" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H83" s="23" t="s">
+      <c r="H84" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="I83" s="23" t="s">
+      <c r="I84" s="23" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="84" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A84" s="10" t="s">
+    <row r="85" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A85" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B85" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C85" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D85" s="4">
         <v>2</v>
       </c>
-      <c r="E84" s="60">
+      <c r="E85" s="60">
         <v>300</v>
       </c>
-      <c r="F84" s="58">
+      <c r="F85" s="58">
         <v>0</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G85" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H84" s="4" t="s">
+      <c r="H85" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="I84" s="4" t="s">
+      <c r="I85" s="4" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="85" spans="1:9" s="44" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="45" t="s">
+    <row r="86" spans="1:9" s="44" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="45" t="s">
         <v>400</v>
       </c>
-      <c r="B85" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="C85" s="45" t="s">
+      <c r="B86" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C86" s="45" t="s">
         <v>397</v>
       </c>
-      <c r="D85" s="44">
+      <c r="D86" s="44">
         <v>0</v>
       </c>
-      <c r="E85" s="63">
+      <c r="E86" s="63">
         <v>36</v>
       </c>
-      <c r="F85" s="64">
+      <c r="F86" s="64">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G85" s="44" t="s">
+      <c r="G86" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="H85" s="44" t="s">
+      <c r="H86" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="I85" s="44" t="s">
+      <c r="I86" s="44" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="9" t="s">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C86" s="9" t="s">
+      <c r="B87" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C87" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D87" s="3">
         <v>2</v>
       </c>
-      <c r="E86" s="57">
+      <c r="E87" s="57">
         <v>32</v>
       </c>
-      <c r="F86" s="55">
+      <c r="F87" s="55">
         <f t="shared" si="6"/>
         <v>64</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C87" s="81" t="s">
-        <v>497</v>
-      </c>
-      <c r="D87" s="3">
-        <v>2</v>
-      </c>
-      <c r="E87" s="57">
-        <v>36</v>
-      </c>
-      <c r="F87" s="55">
-        <f t="shared" ref="F87" si="7">E87*D87</f>
-        <v>72</v>
-      </c>
       <c r="G87" s="3" t="s">
         <v>34</v>
       </c>
@@ -4820,582 +4843,584 @@
         <v>204</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
-        <v>257</v>
+        <v>400</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C88" s="9" t="s">
-        <v>258</v>
+      <c r="C88" s="81" t="s">
+        <v>497</v>
       </c>
       <c r="D88" s="3">
         <v>2</v>
       </c>
       <c r="E88" s="57">
+        <v>36</v>
+      </c>
+      <c r="F88" s="55">
+        <f t="shared" ref="F88" si="7">E88*D88</f>
+        <v>72</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D89" s="3">
+        <v>2</v>
+      </c>
+      <c r="E89" s="57">
         <v>2104</v>
       </c>
-      <c r="F88" s="55">
+      <c r="F89" s="55">
         <f t="shared" si="6"/>
         <v>4208</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G89" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="H89" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I88" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="9" t="s">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C89" s="9" t="s">
+      <c r="B90" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C90" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D90" s="3">
         <v>2</v>
       </c>
-      <c r="E89" s="57">
+      <c r="E90" s="57">
         <v>82</v>
       </c>
-      <c r="F89" s="55">
+      <c r="F90" s="55">
         <f t="shared" si="6"/>
         <v>164</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="G90" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="H90" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="I90" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="26" t="s">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C90" s="9" t="s">
+      <c r="B91" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C91" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="D90" s="3">
-        <v>1</v>
-      </c>
-      <c r="E90" s="57">
+      <c r="D91" s="3">
+        <v>1</v>
+      </c>
+      <c r="E91" s="57">
         <v>520</v>
       </c>
-      <c r="F90" s="55">
+      <c r="F91" s="55">
         <f t="shared" si="6"/>
         <v>520</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G91" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="H91" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="I91" s="3" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="91" spans="1:9" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="26" t="s">
+    <row r="92" spans="1:9" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="26" t="s">
         <v>513</v>
       </c>
-      <c r="B91" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C91" s="26" t="s">
+      <c r="B92" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C92" s="26" t="s">
         <v>514</v>
       </c>
-      <c r="D91" s="19">
+      <c r="D92" s="19">
         <v>2</v>
       </c>
-      <c r="E91" s="76">
+      <c r="E92" s="76">
         <v>148</v>
       </c>
-      <c r="F91" s="67">
+      <c r="F92" s="67">
         <f t="shared" si="6"/>
         <v>296</v>
       </c>
-      <c r="G91" s="19" t="s">
+      <c r="G92" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="H91" s="19" t="s">
+      <c r="H92" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="I91" s="19" t="s">
+      <c r="I92" s="19" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="10" t="s">
+    <row r="93" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B93" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C93" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D93" s="3">
         <v>14</v>
       </c>
-      <c r="E92" s="57">
+      <c r="E93" s="57">
         <v>20</v>
       </c>
-      <c r="F92" s="55">
+      <c r="F93" s="55">
         <v>0</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G93" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="H93" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I92" s="4" t="s">
+      <c r="I93" s="4" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="93" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="10" t="s">
+    <row r="94" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B94" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C94" s="10" t="s">
         <v>588</v>
       </c>
-      <c r="D93" s="4">
-        <v>1</v>
-      </c>
-      <c r="E93" s="60">
+      <c r="D94" s="4">
+        <v>1</v>
+      </c>
+      <c r="E94" s="60">
         <v>10</v>
       </c>
-      <c r="F93" s="58">
+      <c r="F94" s="58">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G94" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H93" s="4" t="s">
+      <c r="H94" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="I93" s="4" t="s">
+      <c r="I94" s="4" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="9" t="s">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C94" s="9" t="s">
+      <c r="B95" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C95" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D95" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="57">
+      <c r="E95" s="57">
         <v>28</v>
       </c>
-      <c r="F94" s="55">
+      <c r="F95" s="55">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G95" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="H95" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="I95" s="3" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="95" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="s">
+    <row r="96" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="E95" s="56"/>
-      <c r="F95" s="56"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D96" s="3">
-        <v>1</v>
-      </c>
-      <c r="E96" s="57"/>
-      <c r="I96" s="3" t="s">
-        <v>231</v>
-      </c>
+      <c r="E96" s="56"/>
+      <c r="F96" s="56"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1</v>
+      </c>
+      <c r="E97" s="57"/>
+      <c r="I97" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C97" s="9" t="s">
+      <c r="B98" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C98" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="D97" s="3">
-        <v>1</v>
-      </c>
-      <c r="E97" s="57">
+      <c r="D98" s="3">
+        <v>1</v>
+      </c>
+      <c r="E98" s="57">
         <v>63</v>
-      </c>
-      <c r="F97" s="55">
-        <f>D97*E97</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D98" s="3">
-        <v>2</v>
-      </c>
-      <c r="E98" s="57">
-        <v>69</v>
       </c>
       <c r="F98" s="55">
         <f>D98*E98</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D99" s="3">
+        <v>2</v>
+      </c>
+      <c r="E99" s="57">
+        <v>69</v>
+      </c>
+      <c r="F99" s="55">
+        <f>D99*E99</f>
         <v>138</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B100" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="3">
-        <v>1</v>
-      </c>
-      <c r="E99" s="57"/>
-      <c r="I99" s="3" t="s">
+      <c r="D100" s="3">
+        <v>1</v>
+      </c>
+      <c r="E100" s="57"/>
+      <c r="I100" s="3" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="100" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A100" s="4" t="s">
+    <row r="101" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B101" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C101" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D101" s="4">
         <v>5</v>
       </c>
-      <c r="E100" s="60">
-        <v>1</v>
-      </c>
-      <c r="F100" s="58">
+      <c r="E101" s="60">
+        <v>1</v>
+      </c>
+      <c r="F101" s="58">
         <v>5</v>
       </c>
-      <c r="I100" s="4" t="s">
+      <c r="I101" s="4" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="101" spans="1:10" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
+    <row r="102" spans="1:10" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
         <v>373</v>
-      </c>
-      <c r="E101" s="56"/>
-      <c r="F101" s="56"/>
-    </row>
-    <row r="102" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
-        <v>374</v>
       </c>
       <c r="E102" s="56"/>
       <c r="F102" s="56"/>
     </row>
-    <row r="103" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
+    <row r="103" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E103" s="56"/>
+      <c r="F103" s="56"/>
+    </row>
+    <row r="104" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B104" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C103" s="51" t="s">
+      <c r="C104" s="51" t="s">
         <v>375</v>
       </c>
-      <c r="D103" s="3">
-        <v>1</v>
-      </c>
-      <c r="E103" s="55">
+      <c r="D104" s="3">
+        <v>1</v>
+      </c>
+      <c r="E104" s="55">
         <v>200</v>
       </c>
-      <c r="F103" s="55">
-        <f>E103*D103</f>
+      <c r="F104" s="55">
+        <f>E104*D104</f>
         <v>200</v>
       </c>
-      <c r="I103" s="3" t="s">
+      <c r="I104" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="J103" s="4"/>
-    </row>
-    <row r="104" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="4" t="s">
+      <c r="J104" s="4"/>
+    </row>
+    <row r="105" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B105" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C105" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D105" s="4">
         <v>5</v>
       </c>
-      <c r="E104" s="58">
-        <v>1</v>
-      </c>
-      <c r="F104" s="58">
+      <c r="E105" s="58">
+        <v>1</v>
+      </c>
+      <c r="F105" s="58">
         <v>5</v>
       </c>
-      <c r="I104" s="4" t="s">
+      <c r="I105" s="4" t="s">
         <v>380</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="D105" s="3">
-        <v>1</v>
-      </c>
-      <c r="E105" s="55">
-        <v>26</v>
-      </c>
-      <c r="F105" s="55">
-        <f>E105*D105</f>
-        <v>26</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D106" s="3">
         <v>1</v>
       </c>
       <c r="E106" s="55">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F106" s="55">
         <f>E106*D106</f>
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>433</v>
+        <v>383</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>312</v>
+        <v>384</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="D107" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="55">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F107" s="55">
         <f>E107*D107</f>
+        <v>37</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D108" s="3">
+        <v>2</v>
+      </c>
+      <c r="E108" s="55">
+        <v>24</v>
+      </c>
+      <c r="F108" s="55">
+        <f>E108*D108</f>
         <v>48</v>
       </c>
-      <c r="I107" s="3" t="s">
+      <c r="I108" s="3" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="108" spans="1:10" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A108" s="42" t="s">
+    <row r="109" spans="1:10" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A109" s="42" t="s">
         <v>155</v>
-      </c>
-      <c r="E108" s="65"/>
-      <c r="F108" s="65"/>
-    </row>
-    <row r="109" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="14" t="s">
-        <v>540</v>
       </c>
       <c r="E109" s="65"/>
       <c r="F109" s="65"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
+    <row r="110" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="E110" s="65"/>
+      <c r="F110" s="65"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B111" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="D110" s="3">
-        <v>1</v>
-      </c>
-      <c r="E110" s="55">
+      <c r="D111" s="3">
+        <v>1</v>
+      </c>
+      <c r="E111" s="55">
         <v>625</v>
       </c>
-      <c r="F110" s="55">
-        <f>E110*D110</f>
+      <c r="F111" s="55">
+        <f>E111*D111</f>
         <v>625</v>
       </c>
-      <c r="G110" s="3" t="s">
+      <c r="G111" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I110" s="3" t="s">
+      <c r="I111" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="111" spans="1:10" s="17" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A111" s="16" t="s">
+    <row r="112" spans="1:10" s="17" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A112" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="E111" s="66"/>
-      <c r="F111" s="66"/>
-    </row>
-    <row r="112" spans="1:10" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A112" s="20" t="s">
+      <c r="E112" s="66"/>
+      <c r="F112" s="66"/>
+    </row>
+    <row r="113" spans="1:9" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A113" s="20" t="s">
         <v>447</v>
-      </c>
-      <c r="B112" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="C112" s="70" t="s">
-        <v>448</v>
-      </c>
-      <c r="D112" s="19">
-        <v>1</v>
-      </c>
-      <c r="E112" s="67">
-        <v>900</v>
-      </c>
-      <c r="F112" s="67">
-        <f t="shared" ref="F112:F118" si="8">E112*D112</f>
-        <v>900</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I112" s="19" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A113" s="21" t="s">
-        <v>451</v>
       </c>
       <c r="B113" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="C113" s="71" t="s">
+      <c r="C113" s="70" t="s">
+        <v>448</v>
+      </c>
+      <c r="D113" s="19">
+        <v>1</v>
+      </c>
+      <c r="E113" s="67">
+        <v>900</v>
+      </c>
+      <c r="F113" s="67">
+        <f t="shared" ref="F113:F119" si="8">E113*D113</f>
+        <v>900</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="19" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A114" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="C114" s="71" t="s">
         <v>449</v>
       </c>
-      <c r="D113" s="3">
-        <v>1</v>
-      </c>
-      <c r="E113" s="55">
+      <c r="D114" s="3">
+        <v>1</v>
+      </c>
+      <c r="E114" s="55">
         <v>767</v>
       </c>
-      <c r="F113" s="67">
+      <c r="F114" s="67">
         <f t="shared" si="8"/>
         <v>767</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H113" s="19"/>
-      <c r="I113" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A114" s="21" t="s">
-        <v>452</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="C114" s="71" t="s">
-        <v>450</v>
-      </c>
-      <c r="D114" s="3">
-        <v>0</v>
-      </c>
-      <c r="E114" s="55">
-        <v>1540</v>
-      </c>
-      <c r="F114" s="67">
-        <f t="shared" si="8"/>
-        <v>0</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>13</v>
@@ -5406,24 +5431,24 @@
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
-        <v>454</v>
+      <c r="A115" s="21" t="s">
+        <v>452</v>
       </c>
       <c r="B115" s="19" t="s">
         <v>293</v>
       </c>
       <c r="C115" s="71" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D115" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" s="55">
-        <v>877</v>
+        <v>1540</v>
       </c>
       <c r="F115" s="67">
         <f t="shared" si="8"/>
-        <v>877</v>
+        <v>0</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>13</v>
@@ -5435,776 +5460,783 @@
     </row>
     <row r="116" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B116" s="19" t="s">
         <v>293</v>
       </c>
       <c r="C116" s="71" t="s">
-        <v>389</v>
+        <v>453</v>
       </c>
       <c r="D116" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="55">
-        <v>4700</v>
+        <v>877</v>
       </c>
       <c r="F116" s="67">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H116" s="19"/>
       <c r="I116" s="3" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>459</v>
+        <v>293</v>
+      </c>
+      <c r="C117" s="71" t="s">
+        <v>389</v>
       </c>
       <c r="D117" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" s="55">
-        <v>20</v>
+        <v>4700</v>
       </c>
       <c r="F117" s="67">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H117" s="19"/>
       <c r="I117" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C118" s="27" t="s">
-        <v>461</v>
+      <c r="C118" s="3" t="s">
+        <v>459</v>
       </c>
       <c r="D118" s="3">
         <v>1</v>
       </c>
       <c r="E118" s="55">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F118" s="67">
         <f t="shared" si="8"/>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H118" s="19"/>
       <c r="I118" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>461</v>
+      </c>
+      <c r="D119" s="3">
+        <v>1</v>
+      </c>
+      <c r="E119" s="55">
+        <v>25</v>
+      </c>
+      <c r="F119" s="67">
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H119" s="19"/>
+      <c r="I119" s="3" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="119" spans="1:9" s="17" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A119" s="16" t="s">
+    <row r="120" spans="1:9" s="17" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A120" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="E119" s="66"/>
-      <c r="F119" s="66"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
+      <c r="E120" s="66"/>
+      <c r="F120" s="66"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="B120" s="19" t="s">
+      <c r="B121" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="C120" s="52" t="s">
+      <c r="C121" s="52" t="s">
         <v>322</v>
       </c>
-      <c r="D120" s="3">
-        <v>1</v>
-      </c>
-      <c r="E120" s="55">
+      <c r="D121" s="3">
+        <v>1</v>
+      </c>
+      <c r="E121" s="55">
         <v>752</v>
       </c>
-      <c r="F120" s="55">
-        <f t="shared" ref="F120:F125" si="9">D120*E120</f>
+      <c r="F121" s="55">
+        <f t="shared" ref="F121:F126" si="9">D121*E121</f>
         <v>752</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="G121" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I120" s="3" t="s">
+      <c r="I121" s="3" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="121" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A121" s="4" t="s">
+    <row r="122" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B121" s="48" t="s">
+      <c r="B122" s="48" t="s">
         <v>209</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C122" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D121" s="4">
+      <c r="D122" s="4">
         <v>5</v>
       </c>
-      <c r="E121" s="58">
-        <v>1</v>
-      </c>
-      <c r="F121" s="58">
+      <c r="E122" s="58">
+        <v>1</v>
+      </c>
+      <c r="F122" s="58">
         <v>5</v>
       </c>
-      <c r="G121" s="4" t="s">
+      <c r="G122" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I121" s="4" t="s">
+      <c r="I122" s="4" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B122" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C122" s="3" t="s">
+      <c r="B123" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="D122" s="3">
-        <v>1</v>
-      </c>
-      <c r="E122" s="55">
+      <c r="D123" s="3">
+        <v>1</v>
+      </c>
+      <c r="E123" s="55">
         <v>65</v>
       </c>
-      <c r="F122" s="55">
+      <c r="F123" s="55">
         <f t="shared" si="9"/>
         <v>65</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="G123" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I122" s="3" t="s">
+      <c r="I123" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B123" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C123" s="3" t="s">
+      <c r="B124" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D123" s="3">
-        <v>1</v>
-      </c>
-      <c r="E123" s="55">
+      <c r="D124" s="3">
+        <v>1</v>
+      </c>
+      <c r="E124" s="55">
         <v>32</v>
       </c>
-      <c r="F123" s="55">
+      <c r="F124" s="55">
         <f t="shared" si="9"/>
         <v>32</v>
       </c>
-      <c r="G123" s="3" t="s">
+      <c r="G124" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I123" s="3" t="s">
+      <c r="I124" s="3" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B124" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C124" s="3" t="s">
+      <c r="B125" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="D124" s="3">
-        <v>1</v>
-      </c>
-      <c r="E124" s="55">
+      <c r="D125" s="3">
+        <v>1</v>
+      </c>
+      <c r="E125" s="55">
         <v>112</v>
       </c>
-      <c r="F124" s="55">
+      <c r="F125" s="55">
         <f t="shared" si="9"/>
         <v>112</v>
       </c>
-      <c r="G124" s="3" t="s">
+      <c r="G125" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I124" s="3" t="s">
+      <c r="I125" s="3" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="125" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A125" s="4" t="s">
+    <row r="126" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A126" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="B125" s="48" t="s">
+      <c r="B126" s="48" t="s">
         <v>209</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C126" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="D125" s="4">
+      <c r="D126" s="4">
         <v>5</v>
       </c>
-      <c r="E125" s="58">
+      <c r="E126" s="58">
         <v>2</v>
       </c>
-      <c r="F125" s="58">
+      <c r="F126" s="58">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="G125" s="4" t="s">
+      <c r="G126" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I125" s="4" t="s">
+      <c r="I126" s="4" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="126" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A126" s="5" t="s">
+    <row r="127" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A127" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E126" s="56"/>
-      <c r="F126" s="56"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D127" s="3">
-        <v>1</v>
-      </c>
-      <c r="E127" s="55">
-        <v>5420</v>
-      </c>
-      <c r="F127" s="55">
-        <f t="shared" ref="F127:F140" si="10">E127*D127</f>
-        <v>5420</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I127" s="3" t="s">
-        <v>446</v>
-      </c>
+      <c r="E127" s="56"/>
+      <c r="F127" s="56"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C128" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D128" s="3">
+        <v>1</v>
+      </c>
+      <c r="E128" s="55">
+        <v>5420</v>
+      </c>
+      <c r="F128" s="55">
+        <f t="shared" ref="F128:F141" si="10">E128*D128</f>
+        <v>5420</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D128" s="3">
-        <v>1</v>
-      </c>
-      <c r="E128" s="55">
+      <c r="D129" s="3">
+        <v>1</v>
+      </c>
+      <c r="E129" s="55">
         <v>2560</v>
       </c>
-      <c r="F128" s="55">
+      <c r="F129" s="55">
         <f t="shared" si="10"/>
         <v>2560</v>
       </c>
-      <c r="G128" s="3" t="s">
+      <c r="G129" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I128" s="3" t="s">
+      <c r="I129" s="3" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B130" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C130" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="D129" s="3">
-        <v>1</v>
-      </c>
-      <c r="E129" s="55">
+      <c r="D130" s="3">
+        <v>1</v>
+      </c>
+      <c r="E130" s="55">
         <v>900</v>
       </c>
-      <c r="F129" s="55">
+      <c r="F130" s="55">
         <f t="shared" si="10"/>
         <v>900</v>
       </c>
-      <c r="G129" s="3" t="s">
+      <c r="G130" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I129" s="3" t="s">
+      <c r="I130" s="3" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B131" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="C131" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D130" s="3">
-        <v>1</v>
-      </c>
-      <c r="E130" s="55">
+      <c r="D131" s="3">
+        <v>1</v>
+      </c>
+      <c r="E131" s="55">
         <v>163</v>
       </c>
-      <c r="F130" s="55">
+      <c r="F131" s="55">
         <f t="shared" si="10"/>
         <v>163</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="G131" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I130" s="3" t="s">
+      <c r="I131" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B132" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C132" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D131" s="3">
-        <v>1</v>
-      </c>
-      <c r="E131" s="55">
+      <c r="D132" s="3">
+        <v>1</v>
+      </c>
+      <c r="E132" s="55">
         <v>11</v>
       </c>
-      <c r="F131" s="55">
+      <c r="F132" s="55">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="G132" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B133" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="C133" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D132" s="3">
-        <v>1</v>
-      </c>
-      <c r="E132" s="55">
+      <c r="D133" s="3">
+        <v>1</v>
+      </c>
+      <c r="E133" s="55">
         <v>520</v>
       </c>
-      <c r="F132" s="55">
+      <c r="F133" s="55">
         <f t="shared" si="10"/>
         <v>520</v>
       </c>
-      <c r="G132" s="3" t="s">
+      <c r="G133" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B134" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="C134" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D133" s="3">
-        <v>1</v>
-      </c>
-      <c r="E133" s="55">
+      <c r="D134" s="3">
+        <v>1</v>
+      </c>
+      <c r="E134" s="55">
         <v>193</v>
       </c>
-      <c r="F133" s="55">
+      <c r="F134" s="55">
         <f t="shared" si="10"/>
         <v>193</v>
       </c>
-      <c r="G133" s="3" t="s">
+      <c r="G134" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I133" s="3" t="s">
+      <c r="I134" s="3" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B134" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C134" s="3" t="s">
+      <c r="B135" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D135" s="3">
         <v>10</v>
       </c>
-      <c r="E134" s="55">
+      <c r="E135" s="55">
         <v>12</v>
       </c>
-      <c r="F134" s="55">
+      <c r="F135" s="55">
         <f t="shared" si="10"/>
         <v>120</v>
       </c>
-      <c r="G134" s="3" t="s">
+      <c r="G135" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I134" s="3" t="s">
+      <c r="I135" s="3" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C135" s="3" t="s">
+      <c r="B136" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D135" s="3">
-        <v>1</v>
-      </c>
-      <c r="E135" s="55">
+      <c r="D136" s="3">
+        <v>1</v>
+      </c>
+      <c r="E136" s="55">
         <v>14</v>
       </c>
-      <c r="F135" s="55">
+      <c r="F136" s="55">
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G136" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I135" s="3" t="s">
+      <c r="I136" s="3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B136" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C136" s="3" t="s">
+      <c r="B137" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D137" s="3">
         <v>5</v>
       </c>
-      <c r="E136" s="55">
+      <c r="E137" s="55">
         <v>15.25</v>
       </c>
-      <c r="F136" s="55">
+      <c r="F137" s="55">
         <f t="shared" si="10"/>
         <v>76.25</v>
       </c>
-      <c r="G136" s="3" t="s">
+      <c r="G137" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="3" t="s">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C137" s="3" t="s">
+      <c r="B138" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D137" s="3">
+      <c r="D138" s="3">
         <v>10</v>
       </c>
-      <c r="E137" s="55">
+      <c r="E138" s="55">
         <v>16.5</v>
       </c>
-      <c r="F137" s="55">
+      <c r="F138" s="55">
         <f t="shared" si="10"/>
         <v>165</v>
       </c>
-      <c r="G137" s="3" t="s">
+      <c r="G138" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C138" s="3" t="s">
+      <c r="B139" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D138" s="3">
+      <c r="D139" s="3">
         <v>10</v>
       </c>
-      <c r="E138" s="55">
+      <c r="E139" s="55">
         <v>24</v>
       </c>
-      <c r="F138" s="55">
+      <c r="F139" s="55">
         <f t="shared" si="10"/>
         <v>240</v>
       </c>
-      <c r="G138" s="3" t="s">
+      <c r="G139" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="3" t="s">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B139" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C139" s="3" t="s">
+      <c r="B140" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D139" s="3">
+      <c r="D140" s="3">
         <v>6</v>
       </c>
-      <c r="E139" s="55">
+      <c r="E140" s="55">
         <v>24</v>
       </c>
-      <c r="F139" s="55">
+      <c r="F140" s="55">
         <f t="shared" si="10"/>
         <v>144</v>
       </c>
-      <c r="G139" s="3" t="s">
+      <c r="G140" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="25" t="s">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="25" t="s">
         <v>579</v>
       </c>
-      <c r="B140" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C140" s="3" t="s">
+      <c r="B141" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="D140" s="3">
-        <v>1</v>
-      </c>
-      <c r="E140" s="55">
+      <c r="D141" s="3">
+        <v>1</v>
+      </c>
+      <c r="E141" s="55">
         <v>11</v>
       </c>
-      <c r="F140" s="55">
+      <c r="F141" s="55">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="G141" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I140" s="3" t="s">
+      <c r="I141" s="3" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A142" s="10"/>
-      <c r="B142" s="10"/>
-      <c r="C142" s="9"/>
-    </row>
-    <row r="143" spans="1:9" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A143" s="7" t="s">
+    <row r="143" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A143" s="10"/>
+      <c r="B143" s="10"/>
+      <c r="C143" s="9"/>
+    </row>
+    <row r="144" spans="1:9" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A144" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="E143" s="56"/>
-      <c r="F143" s="56"/>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D144" s="3">
-        <v>2</v>
-      </c>
-      <c r="E144" s="55">
-        <v>25</v>
-      </c>
-      <c r="F144" s="55">
-        <f t="shared" ref="F144:F169" si="11">E144*D144</f>
-        <v>50</v>
-      </c>
+      <c r="E144" s="56"/>
+      <c r="F144" s="56"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D145" s="3">
+        <v>2</v>
+      </c>
+      <c r="E145" s="55">
+        <v>25</v>
+      </c>
+      <c r="F145" s="55">
+        <f t="shared" ref="F145:F170" si="11">E145*D145</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B145" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C145" s="3" t="s">
+      <c r="B146" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D145" s="3">
-        <v>1</v>
-      </c>
-      <c r="E145" s="55">
+      <c r="D146" s="3">
+        <v>1</v>
+      </c>
+      <c r="E146" s="55">
         <v>85.1</v>
       </c>
-      <c r="F145" s="55">
+      <c r="F146" s="55">
         <f t="shared" si="11"/>
         <v>85.1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="3" t="s">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B146" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C146" s="3" t="s">
+      <c r="B147" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C147" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D146" s="3">
+      <c r="D147" s="3">
         <v>2</v>
       </c>
-      <c r="E146" s="55">
+      <c r="E147" s="55">
         <v>32</v>
       </c>
-      <c r="F146" s="55">
+      <c r="F147" s="55">
         <f t="shared" si="11"/>
         <v>64</v>
       </c>
-      <c r="I146" s="3" t="s">
+      <c r="I147" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="3" t="s">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B147" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C147" s="3" t="s">
+      <c r="B148" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C148" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D147" s="3">
+      <c r="D148" s="3">
         <v>2</v>
       </c>
-      <c r="E147" s="55">
+      <c r="E148" s="55">
         <v>51.58</v>
       </c>
-      <c r="F147" s="55">
+      <c r="F148" s="55">
         <f t="shared" si="11"/>
         <v>103.16</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="3" t="s">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B148" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C148" s="3" t="s">
+      <c r="B149" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C149" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D148" s="3">
-        <v>1</v>
-      </c>
-      <c r="E148" s="55">
+      <c r="D149" s="3">
+        <v>1</v>
+      </c>
+      <c r="E149" s="55">
         <v>60</v>
       </c>
-      <c r="F148" s="55">
+      <c r="F149" s="55">
         <f t="shared" si="11"/>
         <v>60</v>
       </c>
-      <c r="I148" s="3" t="s">
+      <c r="I149" s="3" t="s">
         <v>124</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D149" s="3">
-        <v>1</v>
-      </c>
-      <c r="E149" s="55">
-        <v>136.47999999999999</v>
-      </c>
-      <c r="F149" s="55">
-        <f t="shared" si="11"/>
-        <v>136.47999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>125</v>
+        <v>566</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D150" s="3">
         <v>1</v>
@@ -6219,536 +6251,536 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D151" s="3">
         <v>1</v>
       </c>
       <c r="E151" s="55">
-        <v>60.95</v>
+        <v>136.47999999999999</v>
       </c>
       <c r="F151" s="55">
         <f t="shared" si="11"/>
-        <v>60.95</v>
+        <v>136.47999999999999</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D152" s="3">
         <v>1</v>
       </c>
       <c r="E152" s="55">
-        <v>119.416</v>
+        <v>60.95</v>
       </c>
       <c r="F152" s="55">
         <f t="shared" si="11"/>
-        <v>119.416</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D153" s="3">
         <v>1</v>
       </c>
       <c r="E153" s="55">
-        <v>105.8</v>
+        <v>119.416</v>
       </c>
       <c r="F153" s="55">
         <f t="shared" si="11"/>
-        <v>105.8</v>
+        <v>119.416</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D154" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" s="55">
-        <v>119.6</v>
+        <v>105.8</v>
       </c>
       <c r="F154" s="55">
         <f t="shared" si="11"/>
-        <v>239.2</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="D155" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" s="55">
-        <v>100</v>
+        <v>119.6</v>
       </c>
       <c r="F155" s="55">
         <f t="shared" si="11"/>
-        <v>100</v>
+        <v>239.2</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>136</v>
+        <v>276</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>137</v>
+        <v>277</v>
       </c>
       <c r="D156" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" s="55">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F156" s="55">
         <f t="shared" si="11"/>
-        <v>184</v>
+        <v>100</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D157" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" s="55">
-        <v>96.23</v>
+        <v>92</v>
       </c>
       <c r="F157" s="55">
         <f t="shared" si="11"/>
-        <v>96.23</v>
+        <v>184</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D158" s="3">
         <v>1</v>
       </c>
       <c r="E158" s="55">
-        <v>102.44</v>
+        <v>96.23</v>
       </c>
       <c r="F158" s="55">
         <f t="shared" si="11"/>
-        <v>102.44</v>
+        <v>96.23</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D159" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" s="55">
-        <v>28</v>
+        <v>102.44</v>
       </c>
       <c r="F159" s="55">
         <f t="shared" si="11"/>
-        <v>56</v>
+        <v>102.44</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>548</v>
+        <v>143</v>
       </c>
       <c r="D160" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160" s="55">
-        <v>490</v>
+        <v>28</v>
       </c>
       <c r="F160" s="55">
         <f t="shared" si="11"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D161" s="3">
+        <v>1</v>
+      </c>
+      <c r="E161" s="55">
         <v>490</v>
       </c>
-      <c r="I160" s="3" t="s">
+      <c r="F161" s="55">
+        <f t="shared" si="11"/>
+        <v>490</v>
+      </c>
+      <c r="I161" s="3" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="161" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A161" s="28" t="s">
+    <row r="162" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A162" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="B161" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C161" s="28" t="s">
+      <c r="B162" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C162" s="28" t="s">
         <v>549</v>
       </c>
-      <c r="D161" s="28">
-        <v>1</v>
-      </c>
-      <c r="E161" s="43">
+      <c r="D162" s="28">
+        <v>1</v>
+      </c>
+      <c r="E162" s="43">
         <v>77</v>
       </c>
-      <c r="F161" s="43">
+      <c r="F162" s="43">
         <f t="shared" si="11"/>
         <v>77</v>
       </c>
-      <c r="I161" s="28" t="s">
+      <c r="I162" s="28" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="162" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A162" s="28" t="s">
+    <row r="163" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A163" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="B162" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C162" s="28" t="s">
+      <c r="B163" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C163" s="28" t="s">
         <v>551</v>
       </c>
-      <c r="D162" s="28">
-        <v>1</v>
-      </c>
-      <c r="E162" s="43">
+      <c r="D163" s="28">
+        <v>1</v>
+      </c>
+      <c r="E163" s="43">
         <v>20</v>
       </c>
-      <c r="F162" s="43">
+      <c r="F163" s="43">
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="I162" s="28" t="s">
+      <c r="I163" s="28" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="163" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A163" s="28" t="s">
+    <row r="164" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A164" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B163" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C163" s="28" t="s">
+      <c r="B164" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C164" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="D163" s="28">
-        <v>1</v>
-      </c>
-      <c r="E163" s="43">
+      <c r="D164" s="28">
+        <v>1</v>
+      </c>
+      <c r="E164" s="43">
         <v>177</v>
       </c>
-      <c r="F163" s="43">
+      <c r="F164" s="43">
         <f t="shared" si="11"/>
         <v>177</v>
       </c>
-      <c r="I163" s="28" t="s">
+      <c r="I164" s="28" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="3" t="s">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B164" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C164" s="3" t="s">
+      <c r="B165" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C165" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="D164" s="3">
+      <c r="D165" s="3">
         <v>2</v>
       </c>
-      <c r="E164" s="55">
+      <c r="E165" s="55">
         <v>13</v>
       </c>
-      <c r="F164" s="55">
+      <c r="F165" s="55">
         <f t="shared" si="11"/>
         <v>26</v>
       </c>
-      <c r="I164" s="3" t="s">
+      <c r="I165" s="3" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="3" t="s">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B165" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C165" s="3" t="s">
+      <c r="B166" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C166" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="D165" s="3">
+      <c r="D166" s="3">
         <v>2</v>
       </c>
-      <c r="E165" s="55">
+      <c r="E166" s="55">
         <v>19</v>
       </c>
-      <c r="F165" s="55">
+      <c r="F166" s="55">
         <f t="shared" si="11"/>
         <v>38</v>
       </c>
-      <c r="I165" s="3" t="s">
+      <c r="I166" s="3" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="s">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="B166" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C166" s="3" t="s">
+      <c r="B167" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C167" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="D166" s="3">
-        <v>1</v>
-      </c>
-      <c r="E166" s="55">
+      <c r="D167" s="3">
+        <v>1</v>
+      </c>
+      <c r="E167" s="55">
         <v>12</v>
       </c>
-      <c r="F166" s="55">
+      <c r="F167" s="55">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="I166" s="3" t="s">
+      <c r="I167" s="3" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A167" s="3" t="s">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B167" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C167" s="3" t="s">
+      <c r="B168" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C168" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D167" s="3">
+      <c r="D168" s="3">
         <v>2</v>
       </c>
-      <c r="E167" s="55">
+      <c r="E168" s="55">
         <v>35</v>
       </c>
-      <c r="F167" s="55">
+      <c r="F168" s="55">
         <f t="shared" si="11"/>
         <v>70</v>
       </c>
-      <c r="I167" s="3" t="s">
+      <c r="I168" s="3" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" s="3" t="s">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B168" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C168" s="3" t="s">
+      <c r="B169" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C169" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="D168" s="3">
+      <c r="D169" s="3">
         <v>2</v>
       </c>
-      <c r="E168" s="55">
+      <c r="E169" s="55">
         <v>9</v>
       </c>
-      <c r="F168" s="55">
+      <c r="F169" s="55">
         <f t="shared" si="11"/>
         <v>18</v>
       </c>
-      <c r="I168" s="3" t="s">
+      <c r="I169" s="3" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" s="3" t="s">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B170" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="C170" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="D169" s="3">
+      <c r="D170" s="3">
         <v>0</v>
       </c>
-      <c r="E169" s="55">
+      <c r="E170" s="55">
         <v>520</v>
       </c>
-      <c r="F169" s="55">
+      <c r="F170" s="55">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I169" s="3" t="s">
+      <c r="I170" s="3" t="s">
         <v>564</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C170" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D170" s="3">
-        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C171" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D171" s="3">
-        <v>1</v>
-      </c>
-      <c r="I171" s="3" t="s">
-        <v>146</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C172" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D172" s="3">
+        <v>1</v>
+      </c>
+      <c r="I172" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C173" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D172" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A174" s="7" t="s">
+      <c r="D173" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A175" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B174" s="6" t="s">
+      <c r="B175" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="E174" s="56"/>
-      <c r="F174" s="56"/>
-    </row>
-    <row r="175" spans="1:10" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="3"/>
-      <c r="B175" s="3" t="s">
+      <c r="E175" s="56"/>
+      <c r="F175" s="56"/>
+    </row>
+    <row r="176" spans="1:10" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="3"/>
+      <c r="B176" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C175" s="19" t="s">
+      <c r="C176" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="D175" s="3">
+      <c r="D176" s="3">
         <v>4</v>
       </c>
-      <c r="E175" s="55">
+      <c r="E176" s="55">
         <v>40</v>
-      </c>
-      <c r="F175" s="55">
-        <f>E175*D175</f>
-        <v>160</v>
-      </c>
-      <c r="G175" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="H175" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="I175" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="J175" s="19"/>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B176" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="D176" s="3">
-        <v>2</v>
-      </c>
-      <c r="E176" s="55">
-        <v>515</v>
       </c>
       <c r="F176" s="55">
         <f>E176*D176</f>
-        <v>1030</v>
+        <v>160</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>405</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="H176" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="J176" s="19"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B177" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>263</v>
+        <v>528</v>
       </c>
       <c r="D177" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E177" s="55">
-        <v>25</v>
+        <v>515</v>
       </c>
       <c r="F177" s="55">
         <f>E177*D177</f>
-        <v>100</v>
+        <v>1030</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>405</v>
@@ -6759,17 +6791,17 @@
         <v>150</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D178" s="3">
         <v>4</v>
       </c>
       <c r="E178" s="55">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F178" s="55">
         <f>E178*D178</f>
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>405</v>
@@ -6780,235 +6812,256 @@
         <v>150</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D179" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E179" s="55">
-        <v>121.5</v>
+        <v>28</v>
       </c>
       <c r="F179" s="55">
         <f>E179*D179</f>
-        <v>729</v>
+        <v>112</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="E182" s="50" t="s">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B180" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D180" s="3">
+        <v>6</v>
+      </c>
+      <c r="E180" s="55">
+        <v>121.5</v>
+      </c>
+      <c r="F180" s="55">
+        <f>E180*D180</f>
+        <v>729</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E183" s="50" t="s">
         <v>432</v>
       </c>
-      <c r="F182" s="50">
-        <f>SUM(F3:F180)</f>
-        <v>103251.75149919999</v>
-      </c>
-      <c r="G182" s="3" t="s">
+      <c r="F183" s="50">
+        <f>SUM(F3:F181)</f>
+        <v>136251.75149920007</v>
+      </c>
+      <c r="G183" s="3" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A186" s="49" t="s">
+    <row r="187" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A187" s="49" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A187" s="4" t="s">
+    <row r="188" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B188" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C187" s="4" t="s">
+      <c r="C188" s="4" t="s">
         <v>408</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B188" s="3">
-        <v>14</v>
-      </c>
-      <c r="C188" s="3" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B189" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B190" s="3">
         <v>2</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B191" s="3">
         <v>2</v>
       </c>
       <c r="C191" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B192" s="3">
+        <v>2</v>
+      </c>
+      <c r="C192" s="3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A194" s="49" t="s">
+    <row r="195" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A195" s="49" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A195" s="4" t="s">
+    <row r="196" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B196" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C195" s="4" t="s">
+      <c r="C196" s="4" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="3" t="s">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="B196" s="3">
+      <c r="B197" s="3">
         <v>2</v>
       </c>
-      <c r="C196" s="3" t="s">
+      <c r="C197" s="3" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A197" s="3" t="s">
+    <row r="198" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A198" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B197" s="3">
+      <c r="B198" s="3">
         <v>5</v>
       </c>
-      <c r="C197" s="3" t="s">
+      <c r="C198" s="3" t="s">
         <v>427</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B198" s="3">
-        <v>1</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>508</v>
+        <v>324</v>
       </c>
       <c r="B199" s="3">
         <v>1</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>510</v>
+        <v>428</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B200" s="3">
         <v>1</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B201" s="3">
+        <v>1</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="B201" s="3">
-        <v>1</v>
-      </c>
-      <c r="C201" s="3" t="s">
+      <c r="B202" s="3">
+        <v>1</v>
+      </c>
+      <c r="C202" s="3" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A204" s="49" t="s">
+    <row r="205" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A205" s="49" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A205" s="4" t="s">
+    <row r="206" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A206" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B205" s="4" t="s">
+      <c r="B206" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C205" s="4" t="s">
+      <c r="C206" s="4" t="s">
         <v>408</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="B206" s="3">
-        <v>5</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>148</v>
+        <v>424</v>
       </c>
       <c r="B207" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B208" s="3">
+        <v>3</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B209" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C208" s="3" t="s">
+      <c r="C209" s="3" t="s">
         <v>431</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C112" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C113" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C114" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C115" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C120" r:id="rId5" display="MT-1 Accessory Tube Lens" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C103" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C116" r:id="rId7" xr:uid="{3002EF90-377A-4FAD-A836-B22D0D243A96}"/>
+    <hyperlink ref="C113" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C114" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C115" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C116" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C121" r:id="rId5" display="MT-1 Accessory Tube Lens" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C104" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C117" r:id="rId7" xr:uid="{3002EF90-377A-4FAD-A836-B22D0D243A96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>

--- a/Benchtop-2024(default-version)/parts-list/Benchtop-partslist-latest.xlsx
+++ b/Benchtop-2024(default-version)/parts-list/Benchtop-partslist-latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikita\Documents\GitHub\mesoSPIM-bt-hardware\Benchtop-2024(default-version)\parts-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A86552-FCF6-45BC-9F72-AEE6E4726460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9CBF7F-39C7-49A0-A92E-0E0E9D300304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13584" yWindow="5808" windowWidth="32100" windowHeight="16548" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="1320" windowWidth="34560" windowHeight="18600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="626">
   <si>
     <t xml:space="preserve">Part # </t>
   </si>
@@ -608,12 +608,6 @@
     <t>Adapter with External C-Mount Threads and Internal SM1 Threads, 4.4 mm Spacer</t>
   </si>
   <si>
-    <t>BA1S/M</t>
-  </si>
-  <si>
-    <t>Mounting Base, 25 mm x 58 mm x 10 mm</t>
-  </si>
-  <si>
     <t>Optical cage support, 2 per arm</t>
   </si>
   <si>
@@ -621,12 +615,6 @@
   </si>
   <si>
     <t>Ø12.7 mm Optical Post, SS, M4 Setscrew, M6 Tap, L = 40 mm</t>
-  </si>
-  <si>
-    <t>PH75/M</t>
-  </si>
-  <si>
-    <t>Ø12.7 mm Post Holder, Spring-Loaded Hex-Locking Thumbscrew, L=75 mm</t>
   </si>
   <si>
     <t>Compact 25 mm Travel Linear Translation Stage, Side Micrometer, 1/4"-20 Taps</t>
@@ -1523,9 +1511,6 @@
     <t>Ø12.7 mm Optical Post, SS, M4 Setscrew, M6 Tap, L = 50 mm</t>
   </si>
   <si>
-    <t>Clamping post holders (L=75 mm, excitation objective mount) to optical table</t>
-  </si>
-  <si>
     <t>If DIY, lathe turning or similar machining is required, see /custom-parts/excitation-objective/</t>
   </si>
   <si>
@@ -1981,6 +1966,21 @@
       </rPr>
       <t xml:space="preserve"> Oxxius is a budget laser, with frequent quality issues. See overview at (https://github.com/mesoSPIM/benchtop-hardware/wiki/Laser-selection). Includes switching module between 2 laser ports, controlled by TTL signal. The 405nm is NOT included! A four-laser version is ~35k.</t>
     </r>
+  </si>
+  <si>
+    <t>UPH50/M</t>
+  </si>
+  <si>
+    <t>Ø12.7 mm Universal Post Holder, Spring-Loaded Locking Thumbscrew, L = 50 mm</t>
+  </si>
+  <si>
+    <t>Excitation obj mount, compatible with 3D printed immersion chambers.</t>
+  </si>
+  <si>
+    <t>TR75/M</t>
+  </si>
+  <si>
+    <t>Ø12.7 mm Optical Post, SS, M4 Setscrew, M6 Tap, L = 75 mm</t>
   </si>
 </sst>
 </file>
@@ -2763,7 +2763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J209"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5546875" style="3" customWidth="1"/>
@@ -2781,7 +2781,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="68" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E1" s="69"/>
       <c r="F1" s="69"/>
@@ -2800,10 +2800,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="54" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F2" s="54" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>6</v>
@@ -2843,10 +2843,10 @@
         <v>15000</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2871,13 +2871,13 @@
     </row>
     <row r="8" spans="1:9" s="87" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="87" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B8" s="87" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="D8" s="87">
         <v>2</v>
@@ -2893,12 +2893,12 @@
         <v>34</v>
       </c>
       <c r="I8" s="87" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="89" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B9" s="89" t="s">
         <v>161</v>
@@ -2920,7 +2920,7 @@
         <v>34</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -2932,13 +2932,13 @@
     </row>
     <row r="11" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B11" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D11" s="28">
         <v>0</v>
@@ -2951,10 +2951,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
@@ -2978,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H13" s="28" t="s">
         <v>13</v>
@@ -3032,13 +3032,13 @@
         <v>0</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H14" s="28" t="s">
         <v>13</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
@@ -3062,15 +3062,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B16" s="28" t="s">
         <v>18</v>
@@ -3089,21 +3089,21 @@
         <v>0</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B17" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D17" s="28">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
@@ -3170,21 +3170,21 @@
         <v>0</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I19" s="28" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
@@ -3197,7 +3197,7 @@
         <v>19965</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -3227,21 +3227,21 @@
         <v>0</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="I22" s="28" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B23" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D23" s="28">
         <v>0</v>
@@ -3254,21 +3254,21 @@
         <v>0</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="I23" s="28" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
@@ -3281,7 +3281,7 @@
         <v>6900</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -3290,13 +3290,13 @@
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
@@ -3308,21 +3308,21 @@
         <v>0</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D27" s="4">
         <v>0</v>
@@ -3334,21 +3334,21 @@
         <v>1740</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D28" s="3">
         <v>5</v>
@@ -3361,28 +3361,28 @@
         <v>135</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E29" s="56"/>
       <c r="F29" s="56"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D30" s="3">
         <v>2</v>
@@ -3395,21 +3395,21 @@
         <v>140</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D31" s="3">
         <v>6</v>
@@ -3422,21 +3422,21 @@
         <v>216</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -3449,21 +3449,21 @@
         <v>6</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
@@ -3476,21 +3476,21 @@
         <v>9</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
@@ -3503,21 +3503,21 @@
         <v>43</v>
       </c>
       <c r="G34" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -3530,21 +3530,21 @@
         <v>29</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -3557,21 +3557,21 @@
         <v>195</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="82" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
@@ -3584,7 +3584,7 @@
         <v>10</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="12" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -3596,77 +3596,77 @@
     </row>
     <row r="39" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="86" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="E39" s="59"/>
       <c r="F39" s="59"/>
     </row>
     <row r="40" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="83" t="s">
+        <v>599</v>
+      </c>
+      <c r="B40" s="83" t="s">
         <v>604</v>
-      </c>
-      <c r="B40" s="83" t="s">
-        <v>609</v>
       </c>
       <c r="E40" s="85"/>
       <c r="F40" s="85"/>
     </row>
     <row r="41" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="83" t="s">
+        <v>600</v>
+      </c>
+      <c r="B41" s="83" t="s">
         <v>605</v>
-      </c>
-      <c r="B41" s="83" t="s">
-        <v>610</v>
       </c>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
     </row>
     <row r="42" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="83" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="B42" s="83" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="E42" s="85"/>
       <c r="F42" s="85"/>
     </row>
     <row r="43" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="83" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B43" s="83" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="E43" s="85"/>
       <c r="F43" s="85"/>
     </row>
     <row r="44" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="83" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B44" s="83" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E44" s="85"/>
       <c r="F44" s="85"/>
     </row>
     <row r="45" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="83" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B45" s="83" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E45" s="85"/>
       <c r="F45" s="85"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -3678,13 +3678,13 @@
     </row>
     <row r="48" spans="1:9" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="75" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B48" s="40" t="s">
         <v>54</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D48" s="40">
         <v>1</v>
@@ -3697,21 +3697,21 @@
         <v>728</v>
       </c>
       <c r="G48" s="40" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="I48" s="40" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="75" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B49" s="40" t="s">
         <v>54</v>
       </c>
       <c r="C49" s="40" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D49" s="40">
         <v>1</v>
@@ -3723,10 +3723,10 @@
         <v>33</v>
       </c>
       <c r="G49" s="40" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="I49" s="40" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -3756,7 +3756,7 @@
         <v>181</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -3786,7 +3786,7 @@
         <v>181</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -3816,18 +3816,18 @@
         <v>181</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="D53" s="3">
         <v>2</v>
@@ -3846,18 +3846,18 @@
         <v>181</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="D54" s="3">
         <v>2</v>
@@ -3876,7 +3876,7 @@
         <v>181</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -3887,7 +3887,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="D55" s="3">
         <v>2</v>
@@ -3906,18 +3906,18 @@
         <v>181</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D56" s="3">
         <v>2</v>
@@ -3932,7 +3932,7 @@
         <v>34</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -3940,10 +3940,10 @@
         <v>33</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D57" s="3">
         <v>2</v>
@@ -3967,7 +3967,7 @@
         <v>36</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>37</v>
@@ -3989,18 +3989,18 @@
         <v>35</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>172</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D59" s="3">
         <v>1</v>
@@ -4027,7 +4027,7 @@
         <v>38</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>39</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>54</v>
@@ -4073,7 +4073,7 @@
         <v>34</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -4100,10 +4100,10 @@
         <v>34</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -4130,7 +4130,7 @@
         <v>34</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -4160,7 +4160,7 @@
         <v>184</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>184</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -4217,10 +4217,10 @@
         <v>34</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -4231,7 +4231,7 @@
         <v>54</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D67" s="3">
         <v>4</v>
@@ -4247,10 +4247,10 @@
         <v>34</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -4277,21 +4277,21 @@
         <v>34</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -4307,21 +4307,21 @@
         <v>34</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D70" s="3">
         <v>4</v>
@@ -4337,21 +4337,21 @@
         <v>34</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D71" s="3">
         <v>4</v>
@@ -4367,10 +4367,10 @@
         <v>34</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -4378,7 +4378,7 @@
         <v>91863</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>41</v>
@@ -4390,7 +4390,7 @@
         <v>400</v>
       </c>
       <c r="F72" s="58">
-        <f t="shared" ref="F72:F95" si="6">E72*D72</f>
+        <f t="shared" ref="F72:F94" si="6">E72*D72</f>
         <v>800</v>
       </c>
       <c r="G72" s="4" t="s">
@@ -4400,18 +4400,18 @@
         <v>187</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C73" s="48" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D73" s="4">
         <v>2</v>
@@ -4427,21 +4427,21 @@
         <v>34</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="44" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="45" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B74" s="44" t="s">
         <v>54</v>
       </c>
       <c r="C74" s="45" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D74" s="44">
         <v>0</v>
@@ -4457,22 +4457,22 @@
         <v>34</v>
       </c>
       <c r="H74" s="44" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I74" s="44" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="J74" s="73"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D75" s="3">
         <v>2</v>
@@ -4488,21 +4488,21 @@
         <v>34</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="76" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C76" s="72" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D76" s="4">
         <v>2</v>
@@ -4518,21 +4518,21 @@
         <v>34</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D77" s="3">
         <v>4</v>
@@ -4548,78 +4548,78 @@
         <v>34</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D78" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" s="57">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F78" s="55">
-        <f t="shared" si="6"/>
-        <v>16</v>
+        <f>E78*D78</f>
+        <v>20</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>207</v>
+        <v>471</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
-        <v>194</v>
+        <v>621</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>195</v>
+        <v>622</v>
       </c>
       <c r="D79" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E79" s="57">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F79" s="55">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>193</v>
+        <v>623</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
-        <v>476</v>
+        <v>624</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>477</v>
+        <v>625</v>
       </c>
       <c r="D80" s="3">
         <v>2</v>
@@ -4635,629 +4635,623 @@
         <v>34</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="9" t="s">
-        <v>191</v>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="22" t="s">
+        <v>485</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D81" s="3">
+      <c r="C81" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D81" s="23">
         <v>2</v>
       </c>
-      <c r="E81" s="57">
-        <v>5</v>
-      </c>
-      <c r="F81" s="55">
-        <f>E81*D81</f>
-        <v>10</v>
+      <c r="E81" s="61">
+        <v>398</v>
+      </c>
+      <c r="F81" s="62">
+        <f t="shared" si="6"/>
+        <v>796</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="22" t="s">
-        <v>490</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C82" s="22" t="s">
+      <c r="H81" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="D82" s="23">
+      <c r="I81" s="23" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" s="78" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="46" t="s">
+        <v>530</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C82" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="D82" s="78">
         <v>2</v>
       </c>
-      <c r="E82" s="61">
-        <v>398</v>
-      </c>
-      <c r="F82" s="62">
-        <f t="shared" si="6"/>
-        <v>796</v>
-      </c>
-      <c r="G82" s="3" t="s">
+      <c r="E82" s="79">
+        <v>150</v>
+      </c>
+      <c r="F82" s="80">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H82" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="I82" s="23" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" s="78" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A83" s="46" t="s">
-        <v>535</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="C83" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="D83" s="78">
+      <c r="H82" s="78" t="s">
+        <v>198</v>
+      </c>
+      <c r="I82" s="78" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C83" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D83" s="23">
         <v>2</v>
       </c>
-      <c r="E83" s="79">
-        <v>150</v>
-      </c>
-      <c r="F83" s="80">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H83" s="78" t="s">
-        <v>202</v>
-      </c>
-      <c r="I83" s="78" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C84" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="D84" s="23">
-        <v>2</v>
-      </c>
-      <c r="E84" s="61">
+      <c r="E83" s="61">
         <v>30</v>
       </c>
-      <c r="F84" s="62">
+      <c r="F83" s="62">
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G83" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H84" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="I84" s="23" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="D85" s="4">
+      <c r="H83" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="I83" s="23" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D84" s="4">
         <v>2</v>
       </c>
-      <c r="E85" s="60">
+      <c r="E84" s="60">
         <v>300</v>
       </c>
-      <c r="F85" s="58">
+      <c r="F84" s="58">
         <v>0</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G84" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H85" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" s="44" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A86" s="45" t="s">
-        <v>400</v>
-      </c>
-      <c r="B86" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="C86" s="45" t="s">
-        <v>397</v>
-      </c>
-      <c r="D86" s="44">
+      <c r="H84" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" s="44" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A85" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="B85" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C85" s="45" t="s">
+        <v>393</v>
+      </c>
+      <c r="D85" s="44">
         <v>0</v>
       </c>
-      <c r="E86" s="63">
+      <c r="E85" s="63">
         <v>36</v>
       </c>
-      <c r="F86" s="64">
+      <c r="F85" s="64">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G86" s="44" t="s">
+      <c r="G85" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="H86" s="44" t="s">
-        <v>204</v>
-      </c>
-      <c r="I86" s="44" t="s">
-        <v>502</v>
+      <c r="H85" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="I85" s="44" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="D86" s="3">
+        <v>2</v>
+      </c>
+      <c r="E86" s="57">
+        <v>32</v>
+      </c>
+      <c r="F86" s="55">
+        <f t="shared" si="6"/>
+        <v>64</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
-        <v>499</v>
+        <v>396</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C87" s="9" t="s">
-        <v>500</v>
+      <c r="C87" s="81" t="s">
+        <v>492</v>
       </c>
       <c r="D87" s="3">
         <v>2</v>
       </c>
       <c r="E87" s="57">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F87" s="55">
-        <f t="shared" si="6"/>
-        <v>64</v>
+        <f t="shared" ref="F87" si="7">E87*D87</f>
+        <v>72</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
-        <v>400</v>
+        <v>253</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C88" s="81" t="s">
-        <v>497</v>
+      <c r="C88" s="9" t="s">
+        <v>254</v>
       </c>
       <c r="D88" s="3">
         <v>2</v>
       </c>
       <c r="E88" s="57">
-        <v>36</v>
+        <v>2104</v>
       </c>
       <c r="F88" s="55">
-        <f t="shared" ref="F88" si="7">E88*D88</f>
-        <v>72</v>
+        <f t="shared" si="6"/>
+        <v>4208</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>496</v>
+        <v>395</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D89" s="3">
         <v>2</v>
       </c>
       <c r="E89" s="57">
-        <v>2104</v>
+        <v>82</v>
       </c>
       <c r="F89" s="55">
         <f t="shared" si="6"/>
-        <v>4208</v>
+        <v>164</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>399</v>
+        <v>498</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
-        <v>259</v>
+      <c r="A90" s="26" t="s">
+        <v>411</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>260</v>
+        <v>412</v>
       </c>
       <c r="D90" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" s="57">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="F90" s="55">
         <f t="shared" si="6"/>
-        <v>164</v>
+        <v>520</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>415</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="D91" s="3">
-        <v>1</v>
-      </c>
-      <c r="E91" s="57">
-        <v>520</v>
-      </c>
-      <c r="F91" s="55">
-        <f t="shared" si="6"/>
-        <v>520</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="26" t="s">
-        <v>513</v>
-      </c>
-      <c r="B92" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C92" s="26" t="s">
-        <v>514</v>
-      </c>
-      <c r="D92" s="19">
+        <v>508</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C91" s="26" t="s">
+        <v>509</v>
+      </c>
+      <c r="D91" s="19">
         <v>2</v>
       </c>
-      <c r="E92" s="76">
+      <c r="E91" s="76">
         <v>148</v>
       </c>
-      <c r="F92" s="67">
+      <c r="F91" s="67">
         <f t="shared" si="6"/>
         <v>296</v>
       </c>
-      <c r="G92" s="19" t="s">
+      <c r="G91" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="H92" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="I92" s="19" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H91" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="I91" s="19" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D92" s="3">
+        <v>14</v>
+      </c>
+      <c r="E92" s="57">
+        <v>20</v>
+      </c>
+      <c r="F92" s="55">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
-        <v>532</v>
+        <v>584</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="D93" s="3">
-        <v>14</v>
-      </c>
-      <c r="E93" s="57">
-        <v>20</v>
-      </c>
-      <c r="F93" s="55">
-        <v>0</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A94" s="10" t="s">
-        <v>589</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="D94" s="4">
-        <v>1</v>
-      </c>
-      <c r="E94" s="60">
+        <v>586</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="D93" s="4">
+        <v>1</v>
+      </c>
+      <c r="E93" s="60">
         <v>10</v>
       </c>
-      <c r="F94" s="58">
+      <c r="F93" s="58">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G93" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H94" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="D95" s="3">
+      <c r="H93" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E95" s="57">
+      <c r="E94" s="57">
         <v>28</v>
       </c>
-      <c r="F95" s="55">
+      <c r="F94" s="55">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G94" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H95" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E96" s="56"/>
-      <c r="F96" s="56"/>
+      <c r="H94" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E95" s="56"/>
+      <c r="F95" s="56"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" s="3">
+        <v>1</v>
+      </c>
+      <c r="E96" s="57"/>
+      <c r="I96" s="3" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
-        <v>23</v>
+        <v>220</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="D97" s="3">
         <v>1</v>
       </c>
-      <c r="E97" s="57"/>
-      <c r="I97" s="3" t="s">
-        <v>231</v>
+      <c r="E97" s="57">
+        <v>63</v>
+      </c>
+      <c r="F97" s="55">
+        <f>D97*E97</f>
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="9" t="s">
-        <v>224</v>
+      <c r="A98" s="24" t="s">
+        <v>225</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D98" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="57">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F98" s="55">
         <f>D98*E98</f>
-        <v>63</v>
+        <v>138</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="24" t="s">
-        <v>229</v>
+      <c r="A99" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C99" s="9" t="s">
-        <v>230</v>
+        <v>18</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D99" s="3">
-        <v>2</v>
-      </c>
-      <c r="E99" s="57">
-        <v>69</v>
-      </c>
-      <c r="F99" s="55">
-        <f>D99*E99</f>
-        <v>138</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D100" s="3">
-        <v>1</v>
-      </c>
-      <c r="E100" s="57"/>
-      <c r="I100" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="D101" s="4">
+        <v>1</v>
+      </c>
+      <c r="E99" s="57"/>
+      <c r="I99" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="D100" s="4">
         <v>5</v>
       </c>
-      <c r="E101" s="60">
-        <v>1</v>
-      </c>
-      <c r="F101" s="58">
+      <c r="E100" s="60">
+        <v>1</v>
+      </c>
+      <c r="F100" s="58">
         <v>5</v>
       </c>
-      <c r="I101" s="4" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
-        <v>373</v>
+      <c r="I100" s="4" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E101" s="56"/>
+      <c r="F101" s="56"/>
+    </row>
+    <row r="102" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
+        <v>370</v>
       </c>
       <c r="E102" s="56"/>
       <c r="F102" s="56"/>
     </row>
-    <row r="103" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="6" t="s">
+    <row r="103" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="E103" s="56"/>
-      <c r="F103" s="56"/>
-    </row>
-    <row r="104" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+      <c r="C103" s="51" t="s">
+        <v>371</v>
+      </c>
+      <c r="D103" s="3">
+        <v>1</v>
+      </c>
+      <c r="E103" s="55">
+        <v>200</v>
+      </c>
+      <c r="F103" s="55">
+        <f>E103*D103</f>
+        <v>200</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="J103" s="4"/>
+    </row>
+    <row r="104" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D104" s="4">
+        <v>5</v>
+      </c>
+      <c r="E104" s="58">
+        <v>1</v>
+      </c>
+      <c r="F104" s="58">
+        <v>5</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C104" s="51" t="s">
-        <v>375</v>
-      </c>
-      <c r="D104" s="3">
-        <v>1</v>
-      </c>
-      <c r="E104" s="55">
-        <v>200</v>
-      </c>
-      <c r="F104" s="55">
-        <f>E104*D104</f>
-        <v>200</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J104" s="4"/>
-    </row>
-    <row r="105" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C105" s="4" t="s">
+      <c r="D105" s="3">
+        <v>1</v>
+      </c>
+      <c r="E105" s="55">
+        <v>26</v>
+      </c>
+      <c r="F105" s="55">
+        <f>E105*D105</f>
+        <v>26</v>
+      </c>
+      <c r="I105" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="D105" s="4">
-        <v>5</v>
-      </c>
-      <c r="E105" s="58">
-        <v>1</v>
-      </c>
-      <c r="F105" s="58">
-        <v>5</v>
-      </c>
-      <c r="I105" s="4" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>54</v>
@@ -5269,609 +5263,609 @@
         <v>1</v>
       </c>
       <c r="E106" s="55">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F106" s="55">
         <f>E106*D106</f>
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>383</v>
+        <v>429</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>384</v>
+        <v>308</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>385</v>
+        <v>307</v>
       </c>
       <c r="D107" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="55">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F107" s="55">
         <f>E107*D107</f>
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D108" s="3">
-        <v>2</v>
-      </c>
-      <c r="E108" s="55">
-        <v>24</v>
-      </c>
-      <c r="F108" s="55">
-        <f>E108*D108</f>
-        <v>48</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A109" s="42" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A108" s="42" t="s">
         <v>155</v>
+      </c>
+      <c r="E108" s="65"/>
+      <c r="F108" s="65"/>
+    </row>
+    <row r="109" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="14" t="s">
+        <v>535</v>
       </c>
       <c r="E109" s="65"/>
       <c r="F109" s="65"/>
     </row>
-    <row r="110" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="14" t="s">
-        <v>540</v>
-      </c>
-      <c r="E110" s="65"/>
-      <c r="F110" s="65"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="D111" s="3">
-        <v>1</v>
-      </c>
-      <c r="E111" s="55">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D110" s="3">
+        <v>1</v>
+      </c>
+      <c r="E110" s="55">
         <v>625</v>
       </c>
-      <c r="F111" s="55">
-        <f>E111*D111</f>
+      <c r="F110" s="55">
+        <f>E110*D110</f>
         <v>625</v>
       </c>
-      <c r="G111" s="3" t="s">
+      <c r="G110" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I111" s="3" t="s">
+      <c r="I110" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="112" spans="1:10" s="17" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A112" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="E112" s="66"/>
-      <c r="F112" s="66"/>
-    </row>
-    <row r="113" spans="1:9" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A113" s="20" t="s">
+    <row r="111" spans="1:10" s="17" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A111" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="E111" s="66"/>
+      <c r="F111" s="66"/>
+    </row>
+    <row r="112" spans="1:10" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A112" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="C112" s="70" t="s">
+        <v>444</v>
+      </c>
+      <c r="D112" s="19">
+        <v>1</v>
+      </c>
+      <c r="E112" s="67">
+        <v>900</v>
+      </c>
+      <c r="F112" s="67">
+        <f t="shared" ref="F112:F118" si="8">E112*D112</f>
+        <v>900</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" s="19" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A113" s="21" t="s">
         <v>447</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="C113" s="70" t="s">
-        <v>448</v>
-      </c>
-      <c r="D113" s="19">
-        <v>1</v>
-      </c>
-      <c r="E113" s="67">
-        <v>900</v>
+        <v>289</v>
+      </c>
+      <c r="C113" s="71" t="s">
+        <v>445</v>
+      </c>
+      <c r="D113" s="3">
+        <v>1</v>
+      </c>
+      <c r="E113" s="55">
+        <v>767</v>
       </c>
       <c r="F113" s="67">
-        <f t="shared" ref="F113:F119" si="8">E113*D113</f>
-        <v>900</v>
+        <f t="shared" si="8"/>
+        <v>767</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I113" s="19" t="s">
-        <v>457</v>
+      <c r="H113" s="19"/>
+      <c r="I113" s="3" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="21" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C114" s="71" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D114" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="55">
-        <v>767</v>
+        <v>1540</v>
       </c>
       <c r="F114" s="67">
         <f t="shared" si="8"/>
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H114" s="19"/>
       <c r="I114" s="3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A115" s="21" t="s">
-        <v>452</v>
+      <c r="A115" s="3" t="s">
+        <v>450</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C115" s="71" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D115" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" s="55">
-        <v>1540</v>
+        <v>877</v>
       </c>
       <c r="F115" s="67">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H115" s="19"/>
       <c r="I115" s="3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C116" s="71" t="s">
-        <v>453</v>
+        <v>385</v>
       </c>
       <c r="D116" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" s="55">
-        <v>877</v>
+        <v>4700</v>
       </c>
       <c r="F116" s="67">
         <f t="shared" si="8"/>
-        <v>877</v>
+        <v>0</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H116" s="19"/>
       <c r="I116" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B117" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="C117" s="71" t="s">
-        <v>389</v>
-      </c>
       <c r="D117" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" s="55">
-        <v>4700</v>
+        <v>20</v>
       </c>
       <c r="F117" s="67">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H117" s="19"/>
       <c r="I117" s="3" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B118" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C118" s="3" t="s">
-        <v>459</v>
+      <c r="C118" s="27" t="s">
+        <v>457</v>
       </c>
       <c r="D118" s="3">
         <v>1</v>
       </c>
       <c r="E118" s="55">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F118" s="67">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H118" s="19"/>
       <c r="I118" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" s="17" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A119" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="E119" s="66"/>
+      <c r="F119" s="66"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="C120" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D120" s="3">
+        <v>1</v>
+      </c>
+      <c r="E120" s="55">
+        <v>752</v>
+      </c>
+      <c r="F120" s="55">
+        <f t="shared" ref="F120:F125" si="9">D120*E120</f>
+        <v>752</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B121" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D121" s="4">
+        <v>5</v>
+      </c>
+      <c r="E121" s="58">
+        <v>1</v>
+      </c>
+      <c r="F121" s="58">
+        <v>5</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I121" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="B119" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C119" s="27" t="s">
-        <v>461</v>
-      </c>
-      <c r="D119" s="3">
-        <v>1</v>
-      </c>
-      <c r="E119" s="55">
-        <v>25</v>
-      </c>
-      <c r="F119" s="67">
-        <f t="shared" si="8"/>
-        <v>25</v>
-      </c>
-      <c r="G119" s="3" t="s">
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D122" s="3">
+        <v>1</v>
+      </c>
+      <c r="E122" s="55">
+        <v>65</v>
+      </c>
+      <c r="F122" s="55">
+        <f t="shared" si="9"/>
+        <v>65</v>
+      </c>
+      <c r="G122" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H119" s="19"/>
-      <c r="I119" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" s="17" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A120" s="16" t="s">
-        <v>320</v>
-      </c>
-      <c r="E120" s="66"/>
-      <c r="F120" s="66"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="C121" s="52" t="s">
-        <v>322</v>
-      </c>
-      <c r="D121" s="3">
-        <v>1</v>
-      </c>
-      <c r="E121" s="55">
-        <v>752</v>
-      </c>
-      <c r="F121" s="55">
-        <f t="shared" ref="F121:F126" si="9">D121*E121</f>
-        <v>752</v>
-      </c>
-      <c r="G121" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I121" s="3" t="s">
+      <c r="I122" s="3" t="s">
         <v>323</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A122" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B122" s="48" t="s">
-        <v>209</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="D122" s="4">
-        <v>5</v>
-      </c>
-      <c r="E122" s="58">
-        <v>1</v>
-      </c>
-      <c r="F122" s="58">
-        <v>5</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I122" s="4" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B123" s="19" t="s">
         <v>54</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>584</v>
+        <v>325</v>
       </c>
       <c r="D123" s="3">
         <v>1</v>
       </c>
       <c r="E123" s="55">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F123" s="55">
         <f t="shared" si="9"/>
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B124" s="19" t="s">
         <v>54</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="D124" s="3">
         <v>1</v>
       </c>
       <c r="E124" s="55">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="F124" s="55">
         <f t="shared" si="9"/>
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B125" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D125" s="3">
-        <v>1</v>
-      </c>
-      <c r="E125" s="55">
-        <v>112</v>
-      </c>
-      <c r="F125" s="55">
-        <f t="shared" si="9"/>
-        <v>112</v>
-      </c>
-      <c r="G125" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I125" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A126" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="B126" s="48" t="s">
-        <v>209</v>
-      </c>
-      <c r="C126" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="D126" s="4">
+      <c r="B125" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="D125" s="4">
         <v>5</v>
       </c>
-      <c r="E126" s="58">
+      <c r="E125" s="58">
         <v>2</v>
       </c>
-      <c r="F126" s="58">
+      <c r="F125" s="58">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="G125" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I126" s="4" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A127" s="5" t="s">
+      <c r="I125" s="4" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A126" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E127" s="56"/>
-      <c r="F127" s="56"/>
+      <c r="E126" s="56"/>
+      <c r="F126" s="56"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D127" s="3">
+        <v>1</v>
+      </c>
+      <c r="E127" s="55">
+        <v>5420</v>
+      </c>
+      <c r="F127" s="55">
+        <f t="shared" ref="F127:F140" si="10">E127*D127</f>
+        <v>5420</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>442</v>
+      </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>51</v>
+        <v>167</v>
       </c>
       <c r="D128" s="3">
         <v>1</v>
       </c>
       <c r="E128" s="55">
-        <v>5420</v>
+        <v>2560</v>
       </c>
       <c r="F128" s="55">
-        <f t="shared" ref="F128:F141" si="10">E128*D128</f>
-        <v>5420</v>
+        <f t="shared" si="10"/>
+        <v>2560</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>44</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>446</v>
+        <v>490</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>165</v>
+        <v>563</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>167</v>
+        <v>499</v>
       </c>
       <c r="D129" s="3">
         <v>1</v>
       </c>
       <c r="E129" s="55">
-        <v>2560</v>
+        <v>900</v>
       </c>
       <c r="F129" s="55">
         <f t="shared" si="10"/>
-        <v>2560</v>
+        <v>900</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>44</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>568</v>
+        <v>168</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>504</v>
+        <v>166</v>
       </c>
       <c r="D130" s="3">
         <v>1</v>
       </c>
       <c r="E130" s="55">
-        <v>900</v>
+        <v>163</v>
       </c>
       <c r="F130" s="55">
         <f t="shared" si="10"/>
-        <v>900</v>
+        <v>163</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>44</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>505</v>
+        <v>169</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D131" s="3">
         <v>1</v>
       </c>
       <c r="E131" s="55">
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="F131" s="55">
         <f t="shared" si="10"/>
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I131" s="3" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>164</v>
+        <v>49</v>
       </c>
       <c r="D132" s="3">
         <v>1</v>
       </c>
       <c r="E132" s="55">
-        <v>11</v>
+        <v>520</v>
       </c>
       <c r="F132" s="55">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>520</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>44</v>
@@ -5879,128 +5873,128 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="D133" s="3">
         <v>1</v>
       </c>
       <c r="E133" s="55">
-        <v>520</v>
+        <v>193</v>
       </c>
       <c r="F133" s="55">
         <f t="shared" si="10"/>
-        <v>520</v>
+        <v>193</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="I133" s="3" t="s">
+        <v>614</v>
+      </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>171</v>
+        <v>263</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="D134" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E134" s="55">
-        <v>193</v>
+        <v>12</v>
       </c>
       <c r="F134" s="55">
         <f t="shared" si="10"/>
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>44</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>619</v>
+        <v>262</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D135" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E135" s="55">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F135" s="55">
         <f t="shared" si="10"/>
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>44</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>269</v>
+        <v>562</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>270</v>
+        <v>111</v>
       </c>
       <c r="D136" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E136" s="55">
-        <v>14</v>
+        <v>15.25</v>
       </c>
       <c r="F136" s="55">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>76.25</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I136" s="3" t="s">
-        <v>271</v>
-      </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>567</v>
+        <v>112</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D137" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E137" s="55">
-        <v>15.25</v>
+        <v>16.5</v>
       </c>
       <c r="F137" s="55">
         <f t="shared" si="10"/>
-        <v>76.25</v>
+        <v>165</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>44</v>
@@ -6008,23 +6002,23 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D138" s="3">
         <v>10</v>
       </c>
       <c r="E138" s="55">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="F138" s="55">
         <f t="shared" si="10"/>
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>44</v>
@@ -6032,211 +6026,208 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D139" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E139" s="55">
         <v>24</v>
       </c>
       <c r="F139" s="55">
         <f t="shared" si="10"/>
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="s">
-        <v>110</v>
+      <c r="A140" s="25" t="s">
+        <v>574</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>116</v>
+        <v>575</v>
       </c>
       <c r="D140" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E140" s="55">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F140" s="55">
         <f t="shared" si="10"/>
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="25" t="s">
-        <v>579</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="D141" s="3">
-        <v>1</v>
-      </c>
-      <c r="E141" s="55">
-        <v>11</v>
-      </c>
-      <c r="F141" s="55">
-        <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I141" s="3" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A143" s="10"/>
-      <c r="B143" s="10"/>
-      <c r="C143" s="9"/>
-    </row>
-    <row r="144" spans="1:9" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A144" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="E144" s="56"/>
-      <c r="F144" s="56"/>
+      <c r="I140" s="3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A142" s="10"/>
+      <c r="B142" s="10"/>
+      <c r="C142" s="9"/>
+    </row>
+    <row r="143" spans="1:9" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A143" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="E143" s="56"/>
+      <c r="F143" s="56"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D144" s="3">
+        <v>2</v>
+      </c>
+      <c r="E144" s="55">
+        <v>25</v>
+      </c>
+      <c r="F144" s="55">
+        <f t="shared" ref="F144:F169" si="11">E144*D144</f>
+        <v>50</v>
+      </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>562</v>
+        <v>108</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>561</v>
+        <v>109</v>
       </c>
       <c r="D145" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="55">
-        <v>25</v>
+        <v>85.1</v>
       </c>
       <c r="F145" s="55">
-        <f t="shared" ref="F145:F170" si="11">E145*D145</f>
-        <v>50</v>
+        <f t="shared" si="11"/>
+        <v>85.1</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D146" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" s="55">
-        <v>85.1</v>
+        <v>32</v>
       </c>
       <c r="F146" s="55">
         <f t="shared" si="11"/>
-        <v>85.1</v>
+        <v>64</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D147" s="3">
         <v>2</v>
       </c>
       <c r="E147" s="55">
-        <v>32</v>
+        <v>51.58</v>
       </c>
       <c r="F147" s="55">
         <f t="shared" si="11"/>
-        <v>64</v>
-      </c>
-      <c r="I147" s="3" t="s">
-        <v>119</v>
+        <v>103.16</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D148" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" s="55">
-        <v>51.58</v>
+        <v>60</v>
       </c>
       <c r="F148" s="55">
         <f t="shared" si="11"/>
-        <v>103.16</v>
+        <v>60</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>122</v>
+        <v>561</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D149" s="3">
         <v>1</v>
       </c>
       <c r="E149" s="55">
-        <v>60</v>
+        <v>136.47999999999999</v>
       </c>
       <c r="F149" s="55">
         <f t="shared" si="11"/>
-        <v>60</v>
-      </c>
-      <c r="I149" s="3" t="s">
-        <v>124</v>
+        <v>136.47999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>566</v>
+        <v>125</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D150" s="3">
         <v>1</v>
@@ -6251,539 +6242,539 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D151" s="3">
         <v>1</v>
       </c>
       <c r="E151" s="55">
-        <v>136.47999999999999</v>
+        <v>60.95</v>
       </c>
       <c r="F151" s="55">
         <f t="shared" si="11"/>
-        <v>136.47999999999999</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D152" s="3">
         <v>1</v>
       </c>
       <c r="E152" s="55">
-        <v>60.95</v>
+        <v>119.416</v>
       </c>
       <c r="F152" s="55">
         <f t="shared" si="11"/>
-        <v>60.95</v>
+        <v>119.416</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D153" s="3">
         <v>1</v>
       </c>
       <c r="E153" s="55">
-        <v>119.416</v>
+        <v>105.8</v>
       </c>
       <c r="F153" s="55">
         <f t="shared" si="11"/>
-        <v>119.416</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D154" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" s="55">
-        <v>105.8</v>
+        <v>119.6</v>
       </c>
       <c r="F154" s="55">
         <f t="shared" si="11"/>
-        <v>105.8</v>
+        <v>239.2</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>135</v>
+        <v>273</v>
       </c>
       <c r="D155" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" s="55">
-        <v>119.6</v>
+        <v>100</v>
       </c>
       <c r="F155" s="55">
         <f t="shared" si="11"/>
-        <v>239.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>276</v>
+        <v>136</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>277</v>
+        <v>137</v>
       </c>
       <c r="D156" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" s="55">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F156" s="55">
         <f t="shared" si="11"/>
-        <v>100</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D157" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" s="55">
-        <v>92</v>
+        <v>96.23</v>
       </c>
       <c r="F157" s="55">
         <f t="shared" si="11"/>
-        <v>184</v>
+        <v>96.23</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D158" s="3">
         <v>1</v>
       </c>
       <c r="E158" s="55">
-        <v>96.23</v>
+        <v>102.44</v>
       </c>
       <c r="F158" s="55">
         <f t="shared" si="11"/>
-        <v>96.23</v>
+        <v>102.44</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D159" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" s="55">
-        <v>102.44</v>
+        <v>28</v>
       </c>
       <c r="F159" s="55">
         <f t="shared" si="11"/>
-        <v>102.44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>143</v>
+        <v>543</v>
       </c>
       <c r="D160" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160" s="55">
-        <v>28</v>
+        <v>490</v>
       </c>
       <c r="F160" s="55">
         <f t="shared" si="11"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="D161" s="3">
-        <v>1</v>
-      </c>
-      <c r="E161" s="55">
         <v>490</v>
       </c>
-      <c r="F161" s="55">
+      <c r="I160" s="3" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A161" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B161" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C161" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="D161" s="28">
+        <v>1</v>
+      </c>
+      <c r="E161" s="43">
+        <v>77</v>
+      </c>
+      <c r="F161" s="43">
         <f t="shared" si="11"/>
-        <v>490</v>
-      </c>
-      <c r="I161" s="3" t="s">
-        <v>552</v>
+        <v>77</v>
+      </c>
+      <c r="I161" s="28" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="162" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="28" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B162" s="28" t="s">
         <v>54</v>
       </c>
       <c r="C162" s="28" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D162" s="28">
         <v>1</v>
       </c>
       <c r="E162" s="43">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="F162" s="43">
         <f t="shared" si="11"/>
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="I162" s="28" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="163" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="28" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B163" s="28" t="s">
         <v>54</v>
       </c>
       <c r="C163" s="28" t="s">
-        <v>551</v>
+        <v>61</v>
       </c>
       <c r="D163" s="28">
         <v>1</v>
       </c>
       <c r="E163" s="43">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="F163" s="43">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="I163" s="28" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A164" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B164" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C164" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="D164" s="28">
-        <v>1</v>
-      </c>
-      <c r="E164" s="43">
-        <v>177</v>
-      </c>
-      <c r="F164" s="43">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D164" s="3">
+        <v>2</v>
+      </c>
+      <c r="E164" s="55">
+        <v>13</v>
+      </c>
+      <c r="F164" s="55">
         <f t="shared" si="11"/>
-        <v>177</v>
-      </c>
-      <c r="I164" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I164" s="3" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D165" s="3">
         <v>2</v>
       </c>
       <c r="E165" s="55">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F165" s="55">
         <f t="shared" si="11"/>
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>87</v>
+        <v>552</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D166" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" s="55">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F166" s="55">
         <f t="shared" si="11"/>
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>557</v>
+        <v>80</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>556</v>
+        <v>81</v>
       </c>
       <c r="D167" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" s="55">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F167" s="55">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>80</v>
+        <v>564</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>81</v>
+        <v>565</v>
       </c>
       <c r="D168" s="3">
         <v>2</v>
       </c>
       <c r="E168" s="55">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F168" s="55">
         <f t="shared" si="11"/>
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>54</v>
+        <v>553</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="D169" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E169" s="55">
-        <v>9</v>
+        <v>520</v>
       </c>
       <c r="F169" s="55">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>558</v>
-      </c>
       <c r="C170" s="3" t="s">
-        <v>559</v>
+        <v>144</v>
       </c>
       <c r="D170" s="3">
-        <v>0</v>
-      </c>
-      <c r="E170" s="55">
-        <v>520</v>
-      </c>
-      <c r="F170" s="55">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I170" s="3" t="s">
-        <v>564</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C171" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D171" s="3">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C172" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D172" s="3">
         <v>1</v>
       </c>
-      <c r="I172" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C173" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D173" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A175" s="7" t="s">
+    </row>
+    <row r="174" spans="1:10" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A174" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B175" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="E175" s="56"/>
-      <c r="F175" s="56"/>
-    </row>
-    <row r="176" spans="1:10" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="3"/>
+      <c r="B174" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E174" s="56"/>
+      <c r="F174" s="56"/>
+    </row>
+    <row r="175" spans="1:10" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="3"/>
+      <c r="B175" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C175" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D175" s="3">
+        <v>4</v>
+      </c>
+      <c r="E175" s="55">
+        <v>40</v>
+      </c>
+      <c r="F175" s="55">
+        <f>E175*D175</f>
+        <v>160</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H175" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J175" s="19"/>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B176" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C176" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>523</v>
       </c>
       <c r="D176" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E176" s="55">
-        <v>40</v>
+        <v>515</v>
       </c>
       <c r="F176" s="55">
         <f>E176*D176</f>
-        <v>160</v>
+        <v>1030</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="H176" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="I176" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="J176" s="19"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B177" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>528</v>
+        <v>259</v>
       </c>
       <c r="D177" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E177" s="55">
-        <v>515</v>
+        <v>25</v>
       </c>
       <c r="F177" s="55">
         <f>E177*D177</f>
-        <v>1030</v>
+        <v>100</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6791,20 +6782,20 @@
         <v>150</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D178" s="3">
         <v>4</v>
       </c>
       <c r="E178" s="55">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F178" s="55">
         <f>E178*D178</f>
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6812,256 +6803,235 @@
         <v>150</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D179" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E179" s="55">
-        <v>28</v>
+        <v>121.5</v>
       </c>
       <c r="F179" s="55">
         <f>E179*D179</f>
-        <v>112</v>
+        <v>729</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B180" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D180" s="3">
-        <v>6</v>
-      </c>
-      <c r="E180" s="55">
-        <v>121.5</v>
-      </c>
-      <c r="F180" s="55">
-        <f>E180*D180</f>
-        <v>729</v>
-      </c>
-      <c r="G180" s="3" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="E183" s="50" t="s">
-        <v>432</v>
-      </c>
-      <c r="F183" s="50">
-        <f>SUM(F3:F181)</f>
-        <v>136251.75149920007</v>
-      </c>
-      <c r="G183" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A187" s="49" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A188" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="B188" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E182" s="50" t="s">
+        <v>428</v>
+      </c>
+      <c r="F182" s="50">
+        <f>SUM(F3:F180)</f>
+        <v>136295.75149920007</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A186" s="49" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C188" s="4" t="s">
-        <v>408</v>
+      <c r="B187" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B188" s="3">
+        <v>14</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B189" s="3">
+        <v>2</v>
+      </c>
+      <c r="C189" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="B189" s="3">
-        <v>14</v>
-      </c>
-      <c r="C189" s="3" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B190" s="3">
         <v>2</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B191" s="3">
         <v>2</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="B192" s="3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A194" s="49" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B196" s="3">
         <v>2</v>
       </c>
-      <c r="C192" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A195" s="49" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A196" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C196" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>421</v>
+        <v>290</v>
       </c>
       <c r="B197" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="B198" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>324</v>
+        <v>503</v>
       </c>
       <c r="B199" s="3">
         <v>1</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>428</v>
+        <v>505</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B200" s="3">
         <v>1</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>511</v>
+        <v>587</v>
       </c>
       <c r="B201" s="3">
         <v>1</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="B202" s="3">
-        <v>1</v>
-      </c>
-      <c r="C202" s="3" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A205" s="49" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A206" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="B206" s="4" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A204" s="49" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C206" s="4" t="s">
-        <v>408</v>
+      <c r="B205" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B206" s="3">
+        <v>5</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>424</v>
+        <v>148</v>
       </c>
       <c r="B207" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B208" s="3">
-        <v>3</v>
+        <v>426</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C209" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C113" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C114" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C115" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C116" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C121" r:id="rId5" display="MT-1 Accessory Tube Lens" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C104" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C117" r:id="rId7" xr:uid="{3002EF90-377A-4FAD-A836-B22D0D243A96}"/>
+    <hyperlink ref="C112" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C113" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C114" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C115" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C120" r:id="rId5" display="MT-1 Accessory Tube Lens" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C103" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C116" r:id="rId7" xr:uid="{3002EF90-377A-4FAD-A836-B22D0D243A96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>
@@ -7139,7 +7109,7 @@
         <v>7400</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
@@ -7160,15 +7130,15 @@
         <v>20000</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D5" s="28">
         <v>1</v>
@@ -7180,17 +7150,17 @@
         <v>50000</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -7213,31 +7183,31 @@
         <v>25000</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:9" s="17" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:9" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="28" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D12" s="28">
         <v>1</v>
@@ -7253,21 +7223,21 @@
         <v>13</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="28" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D13" s="28">
         <v>1</v>
@@ -7283,21 +7253,21 @@
         <v>13</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B14" s="29" t="s">
         <v>54</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D14" s="28">
         <v>1</v>
@@ -7313,21 +7283,21 @@
         <v>13</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B15" s="29" t="s">
         <v>54</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D15" s="28">
         <v>1</v>
@@ -7343,21 +7313,21 @@
         <v>13</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="29" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D16" s="29">
         <v>1</v>
@@ -7373,32 +7343,32 @@
         <v>13</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:10" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>14</v>
@@ -7423,13 +7393,13 @@
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -7451,13 +7421,13 @@
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
@@ -7478,13 +7448,13 @@
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -7492,32 +7462,32 @@
       <c r="E22" s="41"/>
       <c r="F22" s="41"/>
       <c r="I22" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:10" s="37" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="36" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38"/>
     </row>
     <row r="26" spans="1:10" s="29" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D26" s="29">
         <v>2</v>
@@ -7533,21 +7503,21 @@
         <v>34</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I26" s="29" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="29" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="C27" s="32" t="s">
         <v>285</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>289</v>
       </c>
       <c r="D27" s="29">
         <v>2</v>
@@ -7563,21 +7533,21 @@
         <v>34</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I27" s="29" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="29" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D28" s="29">
         <v>8</v>
@@ -7593,21 +7563,21 @@
         <v>34</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I28" s="29" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="29" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="32" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B29" s="29" t="s">
         <v>54</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D29" s="29">
         <v>6</v>
@@ -7623,18 +7593,18 @@
         <v>34</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="29" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="32" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D30" s="29">
         <v>2</v>
@@ -7650,21 +7620,21 @@
         <v>34</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I30" s="29" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="29" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D31" s="29">
         <v>1</v>
@@ -7680,21 +7650,21 @@
         <v>34</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="29" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="B32" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="32" t="s">
         <v>287</v>
-      </c>
-      <c r="B32" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="C32" s="32" t="s">
-        <v>291</v>
       </c>
       <c r="D32" s="29">
         <v>1</v>
@@ -7710,21 +7680,21 @@
         <v>34</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I32" s="29" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="29" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="32" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B33" s="29" t="s">
         <v>54</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D33" s="29">
         <v>2</v>
@@ -7740,7 +7710,7 @@
         <v>34</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -7774,12 +7744,12 @@
         <v>44</v>
       </c>
       <c r="I38" s="28" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -8281,7 +8251,7 @@
     </row>
     <row r="66" spans="1:10" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F66" s="8"/>
     </row>
@@ -8306,18 +8276,18 @@
         <v>280</v>
       </c>
       <c r="I67" s="28" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D68" s="28">
         <v>2</v>
@@ -8330,18 +8300,18 @@
         <v>168</v>
       </c>
       <c r="I68" s="28" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D69" s="28">
         <v>1</v>
@@ -8354,18 +8324,18 @@
         <v>54</v>
       </c>
       <c r="I69" s="28" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="6" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F71" s="8"/>
     </row>
     <row r="72" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C72" s="29"/>
       <c r="E72" s="31"/>
@@ -8374,7 +8344,7 @@
     </row>
     <row r="73" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="28" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C73" s="29"/>
       <c r="E73" s="31"/>
@@ -8392,20 +8362,20 @@
         <v>149</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
     </row>
     <row r="76" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B76" s="28" t="s">
         <v>150</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D76" s="28">
         <v>1</v>
@@ -8423,13 +8393,13 @@
     </row>
     <row r="77" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="28" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B77" s="28" t="s">
         <v>150</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D77" s="28">
         <v>1</v>
@@ -8444,13 +8414,13 @@
     </row>
     <row r="78" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B78" s="28" t="s">
         <v>150</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D78" s="28">
         <v>1</v>
@@ -8468,13 +8438,13 @@
     </row>
     <row r="79" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="28" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B79" s="28" t="s">
         <v>150</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D79" s="28">
         <v>1</v>
@@ -8489,13 +8459,13 @@
     </row>
     <row r="80" spans="1:10" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B80" s="28" t="s">
         <v>150</v>
       </c>
       <c r="C80" s="28" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D80" s="28">
         <v>1</v>
@@ -8510,13 +8480,13 @@
     </row>
     <row r="81" spans="1:6" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="28" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B81" s="28" t="s">
         <v>150</v>
       </c>
       <c r="C81" s="28" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D81" s="28">
         <v>1</v>
@@ -8531,13 +8501,13 @@
     </row>
     <row r="82" spans="1:6" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B82" s="28" t="s">
         <v>150</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D82" s="28">
         <v>1</v>
@@ -8552,13 +8522,13 @@
     </row>
     <row r="83" spans="1:6" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="28" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B83" s="28" t="s">
         <v>150</v>
       </c>
       <c r="C83" s="28" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D83" s="28">
         <v>1</v>

--- a/Benchtop-2024(default-version)/parts-list/Benchtop-partslist-latest.xlsx
+++ b/Benchtop-2024(default-version)/parts-list/Benchtop-partslist-latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikita\Documents\GitHub\mesoSPIM-bt-hardware\Benchtop-2024(default-version)\parts-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9CBF7F-39C7-49A0-A92E-0E0E9D300304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44385B0C-13D5-4A7E-A0F5-E4854459FF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="1320" windowWidth="34560" windowHeight="18600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10752" yWindow="2388" windowWidth="30156" windowHeight="21264" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="625">
   <si>
     <t xml:space="preserve">Part # </t>
   </si>
@@ -1838,18 +1838,6 @@
     <t>already accounted for, see AB90H, 5x, above</t>
   </si>
   <si>
-    <t>Heat sink for galvo driver, 100x75x25 mm or similar</t>
-  </si>
-  <si>
-    <t>2x-servo-boards-QS-series</t>
-  </si>
-  <si>
-    <t>See /galvo-assembly/heatsink-servo-boards</t>
-  </si>
-  <si>
-    <t>Blank heatsink from Mouser or elsewhere</t>
-  </si>
-  <si>
     <t>RD-PDT-S-to-M4-bolts-Base-H10mm</t>
   </si>
   <si>
@@ -1981,6 +1969,15 @@
   </si>
   <si>
     <t>Ø12.7 mm Optical Post, SS, M4 Setscrew, M6 Tap, L = 75 mm</t>
+  </si>
+  <si>
+    <t>QDM2</t>
+  </si>
+  <si>
+    <t>Heatsink and Mount for QG4, QG5, QS15, QS20, QS30, and QS45 Galvanometer System Servo Drivers</t>
+  </si>
+  <si>
+    <t>For DIY heat sink, see /galvo-assembly/heatsink-servo-boards</t>
   </si>
 </sst>
 </file>
@@ -2871,13 +2868,13 @@
     </row>
     <row r="8" spans="1:9" s="87" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="87" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B8" s="87" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="D8" s="87">
         <v>2</v>
@@ -2893,12 +2890,12 @@
         <v>34</v>
       </c>
       <c r="I8" s="87" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="89" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B9" s="89" t="s">
         <v>161</v>
@@ -2920,7 +2917,7 @@
         <v>34</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -2932,7 +2929,7 @@
     </row>
     <row r="11" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B11" s="28" t="s">
         <v>18</v>
@@ -3070,7 +3067,7 @@
     </row>
     <row r="16" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B16" s="28" t="s">
         <v>18</v>
@@ -3235,13 +3232,13 @@
     </row>
     <row r="23" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B23" s="28" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D23" s="28">
         <v>0</v>
@@ -3452,7 +3449,7 @@
         <v>233</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -3479,7 +3476,7 @@
         <v>233</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -3565,7 +3562,7 @@
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="82" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>205</v>
@@ -3584,7 +3581,7 @@
         <v>10</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="12" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -3596,77 +3593,77 @@
     </row>
     <row r="39" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="86" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="E39" s="59"/>
       <c r="F39" s="59"/>
     </row>
     <row r="40" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="83" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B40" s="83" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E40" s="85"/>
       <c r="F40" s="85"/>
     </row>
     <row r="41" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="83" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B41" s="83" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
     </row>
     <row r="42" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="83" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B42" s="83" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E42" s="85"/>
       <c r="F42" s="85"/>
     </row>
     <row r="43" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="83" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B43" s="83" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E43" s="85"/>
       <c r="F43" s="85"/>
     </row>
     <row r="44" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="83" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B44" s="83" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E44" s="85"/>
       <c r="F44" s="85"/>
     </row>
     <row r="45" spans="1:9" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="83" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B45" s="83" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="E45" s="85"/>
       <c r="F45" s="85"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -4521,7 +4518,7 @@
         <v>203</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -4586,13 +4583,13 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="D79" s="3">
         <v>2</v>
@@ -4608,18 +4605,18 @@
         <v>34</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D80" s="3">
         <v>2</v>
@@ -4635,7 +4632,7 @@
         <v>34</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="81" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4995,34 +4992,34 @@
         <v>526</v>
       </c>
     </row>
-    <row r="93" spans="1:9" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="10" t="s">
-        <v>584</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="D93" s="4">
-        <v>1</v>
-      </c>
-      <c r="E93" s="60">
-        <v>10</v>
-      </c>
-      <c r="F93" s="58">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="D93" s="3">
+        <v>2</v>
+      </c>
+      <c r="E93" s="57">
+        <v>181</v>
+      </c>
+      <c r="F93" s="55">
         <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="G93" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G93" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H93" s="4" t="s">
+      <c r="H93" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="I93" s="4" t="s">
-        <v>585</v>
+      <c r="I93" s="3" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -5895,7 +5892,7 @@
         <v>44</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
@@ -6825,7 +6822,7 @@
       </c>
       <c r="F182" s="50">
         <f>SUM(F3:F180)</f>
-        <v>136295.75149920007</v>
+        <v>136647.75149920007</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>438</v>
@@ -6964,7 +6961,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B201" s="3">
         <v>1</v>
@@ -7155,7 +7152,7 @@
     </row>
     <row r="6" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -7188,7 +7185,7 @@
     </row>
     <row r="9" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25"/>
@@ -7749,7 +7746,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="7" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
